--- a/4502 Takeda.xlsx
+++ b/4502 Takeda.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D80D7C-C7C8-4C35-BAFD-681F053F3EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90825A21-F839-4653-B24C-940DD8151AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35640" yWindow="3080" windowWidth="24000" windowHeight="15320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19890" yWindow="3740" windowWidth="19050" windowHeight="16100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="11" r:id="rId1"/>
@@ -75,7 +75,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CP18" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="CU18" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CP20" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="CU20" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -147,7 +147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CO99" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
+    <comment ref="CT99" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
@@ -243,7 +243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CN103" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
+    <comment ref="CS103" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -269,7 +269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CP103" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000B000000}">
+    <comment ref="CU103" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -293,7 +293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CR103" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000C000000}">
+    <comment ref="CW103" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -341,7 +341,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CN109" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
+    <comment ref="CS109" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -370,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="554">
   <si>
     <t>Name</t>
   </si>
@@ -2011,6 +2011,27 @@
   </si>
   <si>
     <t>Q125</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -2442,13 +2463,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>104</xdr:col>
+      <xdr:col>109</xdr:col>
       <xdr:colOff>58469</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>77519</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>104</xdr:col>
+      <xdr:col>109</xdr:col>
       <xdr:colOff>58469</xdr:colOff>
       <xdr:row>159</xdr:row>
       <xdr:rowOff>13137</xdr:rowOff>
@@ -2492,16 +2513,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>85</xdr:col>
-      <xdr:colOff>61309</xdr:colOff>
+      <xdr:col>89</xdr:col>
+      <xdr:colOff>76251</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>85</xdr:col>
-      <xdr:colOff>61309</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>89</xdr:col>
+      <xdr:colOff>76251</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>7470</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2516,8 +2537,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="49652619" y="0"/>
-          <a:ext cx="0" cy="18638345"/>
+          <a:off x="52101427" y="0"/>
+          <a:ext cx="0" cy="19804529"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2897,22 +2918,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H41"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>91</v>
       </c>
@@ -2926,7 +2947,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
         <v>150</v>
       </c>
@@ -2941,7 +2962,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
         <v>153</v>
       </c>
@@ -2958,12 +2979,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" s="23" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="56" t="s">
         <v>30</v>
       </c>
@@ -2975,7 +2996,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" s="55" t="s">
         <v>400</v>
       </c>
@@ -2989,7 +3010,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="56" t="s">
         <v>465</v>
       </c>
@@ -3006,7 +3027,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
         <v>146</v>
       </c>
@@ -3021,7 +3042,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
         <v>223</v>
       </c>
@@ -3036,7 +3057,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
         <v>480</v>
       </c>
@@ -3056,7 +3077,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" s="25" t="s">
         <v>291</v>
       </c>
@@ -3071,7 +3092,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="56" t="s">
         <v>477</v>
       </c>
@@ -3086,7 +3107,7 @@
       </c>
       <c r="F14" s="26"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="25" t="s">
         <v>194</v>
       </c>
@@ -3099,14 +3120,14 @@
       <c r="E15" s="41"/>
       <c r="F15" s="26"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="56"/>
       <c r="C16" s="26"/>
       <c r="D16" s="41"/>
       <c r="E16" s="41"/>
       <c r="F16" s="26"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>71</v>
       </c>
@@ -3119,7 +3140,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="25" t="s">
         <v>156</v>
       </c>
@@ -3136,7 +3157,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="56" t="s">
         <v>471</v>
       </c>
@@ -3148,7 +3169,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="56" t="s">
         <v>472</v>
       </c>
@@ -3163,7 +3184,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="56" t="s">
         <v>108</v>
       </c>
@@ -3173,7 +3194,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>37</v>
       </c>
@@ -3190,7 +3211,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="56" t="s">
         <v>475</v>
       </c>
@@ -3207,7 +3228,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="56" t="s">
         <v>476</v>
       </c>
@@ -3219,7 +3240,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="56" t="s">
         <v>478</v>
       </c>
@@ -3236,7 +3257,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="56" t="s">
         <v>479</v>
       </c>
@@ -3253,7 +3274,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="56" t="s">
         <v>481</v>
       </c>
@@ -3268,7 +3289,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="56" t="s">
         <v>483</v>
       </c>
@@ -3285,7 +3306,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="25" t="s">
         <v>170</v>
       </c>
@@ -3302,7 +3323,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="25" t="s">
         <v>175</v>
       </c>
@@ -3319,7 +3340,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="56" t="s">
         <v>485</v>
       </c>
@@ -3336,7 +3357,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="56" t="s">
         <v>486</v>
       </c>
@@ -3353,7 +3374,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="25" t="s">
         <v>179</v>
       </c>
@@ -3370,7 +3391,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="25" t="s">
         <v>182</v>
       </c>
@@ -3387,7 +3408,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="25" t="s">
         <v>180</v>
       </c>
@@ -3402,7 +3423,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="25" t="s">
         <v>174</v>
       </c>
@@ -3419,7 +3440,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="5" t="s">
         <v>94</v>
       </c>
@@ -3438,7 +3459,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="56" t="s">
         <v>489</v>
       </c>
@@ -3455,7 +3476,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="56" t="s">
         <v>491</v>
       </c>
@@ -3472,7 +3493,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="25" t="s">
         <v>183</v>
       </c>
@@ -3489,7 +3510,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="5" t="s">
         <v>39</v>
       </c>
@@ -3512,18 +3533,18 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="27" t="s">
         <v>11</v>
       </c>
@@ -3531,7 +3552,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
         <v>12</v>
       </c>
@@ -3539,7 +3560,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
         <v>134</v>
       </c>
@@ -3547,7 +3568,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="27" t="s">
         <v>13</v>
       </c>
@@ -3555,7 +3576,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="27" t="s">
         <v>132</v>
       </c>
@@ -3563,7 +3584,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="27" t="s">
         <v>54</v>
       </c>
@@ -3571,7 +3592,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="27" t="s">
         <v>140</v>
       </c>
@@ -3579,18 +3600,18 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="27" t="s">
         <v>122</v>
       </c>
       <c r="C9" s="27"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C11" s="28" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" s="27" t="s">
         <v>138</v>
       </c>
@@ -3606,18 +3627,18 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>11</v>
       </c>
@@ -3625,12 +3646,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>54</v>
       </c>
@@ -3638,7 +3659,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>230</v>
       </c>
@@ -3654,139 +3675,139 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B3:B33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B3" s="28" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="27" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="27" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="27" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="27" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="27" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="27" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B12" s="28" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="27" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="27" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="27" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="27" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="27" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="27" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="27" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B23" s="28" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="27" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="27" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:2" ht="13" x14ac:dyDescent="0.3">
       <c r="B28" s="28" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="27" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="27" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" s="27" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="27" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="27" t="s">
         <v>279</v>
       </c>
@@ -3800,23 +3821,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:L52"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="17.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="3.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.42578125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="3.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.81640625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="17.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1796875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3.81640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="4.7265625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.26953125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.453125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3840,10 +3861,10 @@
         <v>293</v>
       </c>
       <c r="K2" s="47">
-        <v>15.03</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+        <v>17.239999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
         <v>6</v>
       </c>
@@ -3865,10 +3886,10 @@
         <v>292</v>
       </c>
       <c r="K3" s="14">
-        <v>4333</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+        <v>5648</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>73</v>
       </c>
@@ -3890,13 +3911,13 @@
         <v>48</v>
       </c>
       <c r="K4" s="14">
-        <v>1569</v>
+        <v>1575.062414</v>
       </c>
       <c r="L4" s="53" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
         <v>129</v>
       </c>
@@ -3915,10 +3936,10 @@
       </c>
       <c r="K5" s="14">
         <f>K3*K4</f>
-        <v>6798477</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+        <v>8895952.5142720006</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
         <v>143</v>
       </c>
@@ -3936,13 +3957,14 @@
         <v>50</v>
       </c>
       <c r="K6" s="14">
-        <v>0</v>
+        <f>595054+41888+439941</f>
+        <v>1076883</v>
       </c>
       <c r="L6" s="53" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
         <v>23</v>
       </c>
@@ -3966,13 +3988,14 @@
         <v>51</v>
       </c>
       <c r="K7" s="14">
-        <v>3975500</v>
+        <f>4369681+512157</f>
+        <v>4881838</v>
       </c>
       <c r="L7" s="53" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="20" t="s">
         <v>189</v>
       </c>
@@ -3993,10 +4016,10 @@
       </c>
       <c r="K8" s="14">
         <f>K5-K6+K7</f>
-        <v>10773977</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+        <v>12700907.514272001</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="56" t="s">
         <v>344</v>
       </c>
@@ -4007,7 +4030,7 @@
       <c r="G9" s="6"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="56" t="s">
         <v>535</v>
       </c>
@@ -4022,7 +4045,7 @@
       <c r="G10" s="6"/>
       <c r="H10" s="8"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="56" t="s">
         <v>488</v>
       </c>
@@ -4039,7 +4062,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="20" t="s">
         <v>392</v>
       </c>
@@ -4056,7 +4079,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="25" t="s">
         <v>289</v>
       </c>
@@ -4073,7 +4096,7 @@
       <c r="G13" s="6"/>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>21</v>
       </c>
@@ -4093,7 +4116,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
         <v>236</v>
       </c>
@@ -4115,7 +4138,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:12" ht="13" x14ac:dyDescent="0.3">
       <c r="B16" s="56" t="s">
         <v>149</v>
       </c>
@@ -4133,7 +4156,7 @@
       <c r="H16" s="8"/>
       <c r="K16" s="15"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="56" t="s">
         <v>396</v>
       </c>
@@ -4151,7 +4174,7 @@
       <c r="H17" s="8"/>
       <c r="K17" s="15"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="56" t="s">
         <v>456</v>
       </c>
@@ -4164,7 +4187,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="56" t="s">
         <v>459</v>
       </c>
@@ -4177,7 +4200,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="56" t="s">
         <v>457</v>
       </c>
@@ -4190,7 +4213,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="56" t="s">
         <v>461</v>
       </c>
@@ -4203,7 +4226,7 @@
       <c r="G21" s="6"/>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="56" t="s">
         <v>454</v>
       </c>
@@ -4216,7 +4239,7 @@
       <c r="G22" s="6"/>
       <c r="H22" s="8"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="56" t="s">
         <v>463</v>
       </c>
@@ -4229,7 +4252,7 @@
       <c r="G23" s="6"/>
       <c r="H23" s="8"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="56" t="s">
         <v>482</v>
       </c>
@@ -4246,7 +4269,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="8"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="56" t="s">
         <v>401</v>
       </c>
@@ -4263,7 +4286,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="8"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" ht="13" x14ac:dyDescent="0.3">
       <c r="B26" s="20" t="s">
         <v>395</v>
       </c>
@@ -4280,7 +4303,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="8"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -4292,7 +4315,7 @@
       <c r="H27" s="4"/>
       <c r="K27" s="14"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="56" t="s">
         <v>462</v>
       </c>
@@ -4313,7 +4336,7 @@
       </c>
       <c r="K28" s="14"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="56" t="s">
         <v>444</v>
       </c>
@@ -4332,7 +4355,7 @@
       <c r="G29" s="6"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="56" t="s">
         <v>448</v>
       </c>
@@ -4347,7 +4370,7 @@
       <c r="G30" s="6"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="56" t="s">
         <v>517</v>
       </c>
@@ -4362,7 +4385,7 @@
       <c r="G31" s="6"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="56" t="s">
         <v>498</v>
       </c>
@@ -4377,7 +4400,7 @@
       <c r="G32" s="6"/>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="56" t="s">
         <v>515</v>
       </c>
@@ -4396,7 +4419,7 @@
       <c r="G33" s="6"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="56" t="s">
         <v>520</v>
       </c>
@@ -4411,7 +4434,7 @@
       <c r="G34" s="6"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="56" t="s">
         <v>504</v>
       </c>
@@ -4430,7 +4453,7 @@
       <c r="G35" s="6"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="56" t="s">
         <v>501</v>
       </c>
@@ -4449,7 +4472,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="56" t="s">
         <v>450</v>
       </c>
@@ -4468,7 +4491,7 @@
       <c r="G37" s="6"/>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="56" t="s">
         <v>506</v>
       </c>
@@ -4487,7 +4510,7 @@
       <c r="G38" s="6"/>
       <c r="H38" s="8"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="56" t="s">
         <v>510</v>
       </c>
@@ -4506,7 +4529,7 @@
       <c r="G39" s="6"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="56" t="s">
         <v>521</v>
       </c>
@@ -4523,7 +4546,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="56" t="s">
         <v>524</v>
       </c>
@@ -4538,7 +4561,7 @@
       <c r="G41" s="6"/>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="56" t="s">
         <v>526</v>
       </c>
@@ -4553,7 +4576,7 @@
       <c r="G42" s="6"/>
       <c r="H42" s="8"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="56" t="s">
         <v>531</v>
       </c>
@@ -4568,7 +4591,7 @@
       <c r="G43" s="6"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B44" s="56" t="s">
         <v>529</v>
       </c>
@@ -4583,7 +4606,7 @@
       <c r="G44" s="6"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B45" s="56" t="s">
         <v>533</v>
       </c>
@@ -4598,7 +4621,7 @@
       <c r="G45" s="6"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B46" s="56" t="s">
         <v>440</v>
       </c>
@@ -4617,7 +4640,7 @@
       <c r="G46" s="6"/>
       <c r="H46" s="8"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B47" s="63" t="s">
         <v>494</v>
       </c>
@@ -4634,22 +4657,22 @@
       <c r="G47" s="9"/>
       <c r="H47" s="11"/>
     </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="6:6" ht="13" x14ac:dyDescent="0.3">
       <c r="F49" s="19" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="6:6" ht="13" x14ac:dyDescent="0.3">
       <c r="F50" s="19" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="6:6" ht="13" x14ac:dyDescent="0.3">
       <c r="F51" s="19" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="6:6" ht="13" x14ac:dyDescent="0.3">
       <c r="F52" s="19" t="s">
         <v>290</v>
       </c>
@@ -4672,26 +4695,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DX153"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:EC153"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="1" customWidth="1"/>
-    <col min="3" max="41" width="9.140625" style="30"/>
-    <col min="42" max="49" width="8.85546875" style="30" hidden="1" customWidth="1"/>
-    <col min="50" max="68" width="8.85546875" style="30" customWidth="1"/>
-    <col min="69" max="76" width="9.5703125" style="30" customWidth="1"/>
-    <col min="77" max="85" width="9.42578125" style="30" customWidth="1"/>
-    <col min="86" max="89" width="8.85546875" style="30" customWidth="1"/>
-    <col min="90" max="95" width="9.7109375" style="30" customWidth="1"/>
-    <col min="96" max="96" width="8.85546875" style="30" customWidth="1"/>
-    <col min="97" max="98" width="9.7109375" style="30" customWidth="1"/>
-    <col min="99" max="101" width="9.7109375" style="1" customWidth="1"/>
-    <col min="102" max="106" width="10.5703125" style="1" customWidth="1"/>
-    <col min="107" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="18.54296875" style="1" customWidth="1"/>
+    <col min="3" max="41" width="9.1796875" style="30"/>
+    <col min="42" max="49" width="8.81640625" style="30" hidden="1" customWidth="1"/>
+    <col min="50" max="68" width="8.81640625" style="30" customWidth="1"/>
+    <col min="69" max="76" width="9.54296875" style="30" customWidth="1"/>
+    <col min="77" max="85" width="9.453125" style="30" customWidth="1"/>
+    <col min="86" max="94" width="8.81640625" style="30" customWidth="1"/>
+    <col min="95" max="100" width="9.7265625" style="30" customWidth="1"/>
+    <col min="101" max="101" width="8.81640625" style="30" customWidth="1"/>
+    <col min="102" max="103" width="9.7265625" style="30" customWidth="1"/>
+    <col min="104" max="106" width="9.7265625" style="1" customWidth="1"/>
+    <col min="107" max="111" width="10.54296875" style="1" customWidth="1"/>
+    <col min="112" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:118" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>10</v>
       </c>
@@ -4702,7 +4725,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:118" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="F2" s="30" t="s">
         <v>235</v>
       </c>
@@ -4919,101 +4942,119 @@
       <c r="CG2" s="53" t="s">
         <v>540</v>
       </c>
-      <c r="CH2" s="30">
-        <v>2023</v>
-      </c>
-      <c r="CI2" s="30">
-        <v>2024</v>
-      </c>
-      <c r="CL2" s="30" t="s">
+      <c r="CH2" s="53" t="s">
+        <v>546</v>
+      </c>
+      <c r="CI2" s="53" t="s">
+        <v>548</v>
+      </c>
+      <c r="CJ2" s="53" t="s">
+        <v>549</v>
+      </c>
+      <c r="CK2" s="53" t="s">
+        <v>550</v>
+      </c>
+      <c r="CL2" s="53" t="s">
+        <v>547</v>
+      </c>
+      <c r="CM2" s="53" t="s">
+        <v>551</v>
+      </c>
+      <c r="CN2" s="53" t="s">
+        <v>552</v>
+      </c>
+      <c r="CO2" s="53" t="s">
+        <v>553</v>
+      </c>
+      <c r="CQ2" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="CM2" s="30" t="s">
+      <c r="CR2" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="CN2" s="24" t="s">
+      <c r="CS2" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="CO2" s="24" t="s">
+      <c r="CT2" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="CP2" s="24" t="s">
+      <c r="CU2" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="CQ2" s="24" t="s">
+      <c r="CV2" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="CR2" s="24" t="s">
+      <c r="CW2" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="CS2" s="24" t="s">
+      <c r="CX2" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="CT2" s="53" t="s">
+      <c r="CY2" s="53" t="s">
         <v>405</v>
       </c>
-      <c r="CU2" s="24" t="s">
+      <c r="CZ2" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="CV2" s="24" t="s">
+      <c r="DA2" s="24" t="s">
         <v>407</v>
       </c>
-      <c r="CW2" s="24" t="s">
+      <c r="DB2" s="24" t="s">
         <v>408</v>
       </c>
-      <c r="CX2" s="24" t="s">
+      <c r="DC2" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="CY2" s="24" t="s">
+      <c r="DD2" s="24" t="s">
         <v>410</v>
       </c>
-      <c r="CZ2" s="24" t="s">
+      <c r="DE2" s="24" t="s">
         <v>411</v>
       </c>
-      <c r="DA2" s="24" t="s">
+      <c r="DF2" s="24" t="s">
         <v>412</v>
       </c>
-      <c r="DB2" s="24" t="s">
+      <c r="DG2" s="24" t="s">
         <v>413</v>
       </c>
-      <c r="DC2" s="24" t="s">
+      <c r="DH2" s="24" t="s">
         <v>414</v>
       </c>
-      <c r="DD2" s="24" t="s">
+      <c r="DI2" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="DE2" s="24" t="s">
+      <c r="DJ2" s="24" t="s">
         <v>416</v>
       </c>
-      <c r="DF2" s="24" t="s">
+      <c r="DK2" s="24" t="s">
         <v>417</v>
       </c>
-      <c r="DG2" s="24" t="s">
+      <c r="DL2" s="24" t="s">
         <v>418</v>
       </c>
-      <c r="DH2" s="24" t="s">
+      <c r="DM2" s="24" t="s">
         <v>419</v>
       </c>
-      <c r="DI2" s="24" t="s">
+      <c r="DN2" s="24" t="s">
         <v>420</v>
       </c>
-      <c r="DJ2" s="24" t="s">
+      <c r="DO2" s="24" t="s">
         <v>421</v>
       </c>
-      <c r="DK2" s="24" t="s">
+      <c r="DP2" s="24" t="s">
         <v>422</v>
       </c>
-      <c r="DL2" s="24" t="s">
+      <c r="DQ2" s="24" t="s">
         <v>423</v>
       </c>
-      <c r="DM2" s="24" t="s">
+      <c r="DR2" s="24" t="s">
         <v>424</v>
       </c>
-      <c r="DN2" s="24" t="s">
+      <c r="DS2" s="24" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="3" spans="1:118" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="C3" s="31">
         <v>38961</v>
       </c>
@@ -5263,99 +5304,128 @@
       <c r="CG3" s="31">
         <v>45747</v>
       </c>
-      <c r="CH3" s="31"/>
-      <c r="CI3" s="31"/>
-      <c r="CJ3" s="31"/>
-      <c r="CK3" s="31"/>
+      <c r="CH3" s="31">
+        <f>+CD3+365</f>
+        <v>45838</v>
+      </c>
+      <c r="CI3" s="31">
+        <f>+CE3+365</f>
+        <v>45930</v>
+      </c>
+      <c r="CJ3" s="31">
+        <f>+CF3+365</f>
+        <v>46022</v>
+      </c>
+      <c r="CK3" s="31">
+        <f>+CG3+365</f>
+        <v>46112</v>
+      </c>
       <c r="CL3" s="31">
+        <f>+CH3+365</f>
+        <v>46203</v>
+      </c>
+      <c r="CM3" s="31">
+        <f>+CI3+365</f>
+        <v>46295</v>
+      </c>
+      <c r="CN3" s="31">
+        <f>+CJ3+365</f>
+        <v>46387</v>
+      </c>
+      <c r="CO3" s="31">
+        <f>+CK3+365</f>
+        <v>46477</v>
+      </c>
+      <c r="CP3" s="31"/>
+      <c r="CQ3" s="31">
         <v>39873</v>
       </c>
-      <c r="CM3" s="31">
+      <c r="CR3" s="31">
         <v>40238</v>
       </c>
-      <c r="CN3" s="31">
+      <c r="CS3" s="31">
         <v>40603</v>
       </c>
-      <c r="CO3" s="31">
+      <c r="CT3" s="31">
         <v>40969</v>
       </c>
-      <c r="CP3" s="31">
+      <c r="CU3" s="31">
         <v>41334</v>
       </c>
-      <c r="CQ3" s="31">
+      <c r="CV3" s="31">
         <v>41699</v>
       </c>
-      <c r="CR3" s="31">
+      <c r="CW3" s="31">
         <v>42065</v>
       </c>
-      <c r="CS3" s="31">
+      <c r="CX3" s="31">
         <v>42432</v>
       </c>
-      <c r="CT3" s="31">
+      <c r="CY3" s="31">
         <v>42795</v>
       </c>
-      <c r="CU3" s="31">
+      <c r="CZ3" s="31">
         <v>43161</v>
       </c>
-      <c r="CV3" s="31">
+      <c r="DA3" s="31">
         <v>43527</v>
       </c>
-      <c r="CW3" s="31">
+      <c r="DB3" s="31">
         <v>43921</v>
       </c>
-      <c r="CX3" s="31">
+      <c r="DC3" s="31">
         <v>44286</v>
       </c>
-      <c r="CY3" s="31">
+      <c r="DD3" s="31">
         <v>44651</v>
       </c>
-      <c r="CZ3" s="31">
+      <c r="DE3" s="31">
         <v>45016</v>
       </c>
-      <c r="DA3" s="31">
+      <c r="DF3" s="31">
         <v>45382</v>
       </c>
-      <c r="DB3" s="31">
+      <c r="DG3" s="31">
         <v>45747</v>
       </c>
-      <c r="DC3" s="31">
+      <c r="DH3" s="31">
         <v>46112</v>
       </c>
-      <c r="DD3" s="31">
+      <c r="DI3" s="31">
         <v>46477</v>
       </c>
-      <c r="DE3" s="31">
+      <c r="DJ3" s="31">
         <v>46843</v>
       </c>
-      <c r="DF3" s="31">
+      <c r="DK3" s="31">
         <v>47208</v>
       </c>
-      <c r="DG3" s="31">
+      <c r="DL3" s="31">
         <v>47573</v>
       </c>
-      <c r="DH3" s="31">
+      <c r="DM3" s="31">
         <v>47938</v>
       </c>
-      <c r="DI3" s="31">
+      <c r="DN3" s="31">
         <v>48304</v>
       </c>
-      <c r="DJ3" s="31">
+      <c r="DO3" s="31">
         <v>48669</v>
       </c>
-      <c r="DK3" s="31">
+      <c r="DP3" s="31">
         <v>49034</v>
       </c>
-      <c r="DL3" s="31">
+      <c r="DQ3" s="31">
         <v>49399</v>
       </c>
-      <c r="DM3" s="31">
+      <c r="DR3" s="31">
         <v>49765</v>
       </c>
-      <c r="DN3" s="61">
+      <c r="DS3" s="61">
         <v>50130</v>
       </c>
     </row>
-    <row r="4" spans="1:118" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:123" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="55" t="s">
         <v>88</v>
       </c>
@@ -5547,47 +5617,52 @@
       <c r="CI4" s="66"/>
       <c r="CJ4" s="66"/>
       <c r="CK4" s="66"/>
-      <c r="CL4" s="66">
+      <c r="CL4" s="66"/>
+      <c r="CM4" s="66"/>
+      <c r="CN4" s="66"/>
+      <c r="CO4" s="66"/>
+      <c r="CP4" s="66"/>
+      <c r="CQ4" s="66">
         <f>SUM(J4:M4)</f>
         <v>126100</v>
       </c>
-      <c r="CM4" s="66">
-        <f t="shared" ref="CM4:CM10" si="1">SUM(N4:Q4)</f>
+      <c r="CR4" s="66">
+        <f t="shared" ref="CR4:CR10" si="1">SUM(N4:Q4)</f>
         <v>122200</v>
       </c>
-      <c r="CN4" s="66">
+      <c r="CS4" s="66">
         <f>SUM(R4:U4)</f>
         <v>117600</v>
       </c>
-      <c r="CO4" s="66">
-        <f>SUM(CO5:CO8)</f>
+      <c r="CT4" s="66">
+        <f>SUM(CT5:CT8)</f>
         <v>117600</v>
       </c>
-      <c r="CP4" s="66">
-        <f>CO4*0.9</f>
+      <c r="CU4" s="66">
+        <f>CT4*0.9</f>
         <v>105840</v>
       </c>
-      <c r="CQ4" s="66">
-        <f>CP4*0.9</f>
+      <c r="CV4" s="66">
+        <f>CU4*0.9</f>
         <v>95256</v>
       </c>
-      <c r="CR4" s="53"/>
-      <c r="CS4" s="53"/>
-      <c r="CT4" s="53"/>
-      <c r="CY4" s="62">
+      <c r="CW4" s="53"/>
+      <c r="CX4" s="53"/>
+      <c r="CY4" s="53"/>
+      <c r="DD4" s="62">
         <f>SUM(BR4:BU4)</f>
         <v>106400</v>
       </c>
-      <c r="CZ4" s="62">
+      <c r="DE4" s="62">
         <f>SUM(BV4:BY4)</f>
         <v>111300</v>
       </c>
-      <c r="DA4" s="62">
+      <c r="DF4" s="62">
         <f>SUM(BZ4:CC4)</f>
         <v>107400</v>
       </c>
     </row>
-    <row r="5" spans="1:118" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>110</v>
       </c>
@@ -5728,26 +5803,31 @@
       <c r="CI5" s="39"/>
       <c r="CJ5" s="39"/>
       <c r="CK5" s="39"/>
-      <c r="CL5" s="39">
+      <c r="CL5" s="39"/>
+      <c r="CM5" s="39"/>
+      <c r="CN5" s="39"/>
+      <c r="CO5" s="39"/>
+      <c r="CP5" s="39"/>
+      <c r="CQ5" s="39">
         <f>SUM(J5:M5)</f>
         <v>66300</v>
       </c>
-      <c r="CM5" s="39">
+      <c r="CR5" s="39">
         <f t="shared" si="1"/>
         <v>67100</v>
       </c>
-      <c r="CN5" s="39">
+      <c r="CS5" s="39">
         <f>SUM(R5:U5)</f>
         <v>64900</v>
       </c>
-      <c r="CO5" s="34">
+      <c r="CT5" s="34">
         <f>SUM(V5:Y5)</f>
         <v>64900</v>
       </c>
-      <c r="CP5" s="34"/>
-      <c r="CQ5" s="34"/>
-    </row>
-    <row r="6" spans="1:118" x14ac:dyDescent="0.2">
+      <c r="CU5" s="34"/>
+      <c r="CV5" s="34"/>
+    </row>
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>112</v>
       </c>
@@ -5885,26 +5965,31 @@
       <c r="CI6" s="39"/>
       <c r="CJ6" s="39"/>
       <c r="CK6" s="39"/>
-      <c r="CL6" s="39">
+      <c r="CL6" s="39"/>
+      <c r="CM6" s="39"/>
+      <c r="CN6" s="39"/>
+      <c r="CO6" s="39"/>
+      <c r="CP6" s="39"/>
+      <c r="CQ6" s="39">
         <f>SUM(J6:M6)</f>
         <v>17200</v>
       </c>
-      <c r="CM6" s="39">
+      <c r="CR6" s="39">
         <f t="shared" si="1"/>
         <v>15800</v>
       </c>
-      <c r="CN6" s="39">
+      <c r="CS6" s="39">
         <f>SUM(R6:U6)</f>
         <v>16200</v>
       </c>
-      <c r="CO6" s="34">
+      <c r="CT6" s="34">
         <f>SUM(V6:Y6)</f>
         <v>16200</v>
       </c>
-      <c r="CP6" s="34"/>
-      <c r="CQ6" s="34"/>
-    </row>
-    <row r="7" spans="1:118" x14ac:dyDescent="0.2">
+      <c r="CU6" s="34"/>
+      <c r="CV6" s="34"/>
+    </row>
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>113</v>
       </c>
@@ -6042,26 +6127,31 @@
       <c r="CI7" s="39"/>
       <c r="CJ7" s="39"/>
       <c r="CK7" s="39"/>
-      <c r="CL7" s="39">
+      <c r="CL7" s="39"/>
+      <c r="CM7" s="39"/>
+      <c r="CN7" s="39"/>
+      <c r="CO7" s="39"/>
+      <c r="CP7" s="39"/>
+      <c r="CQ7" s="39">
         <f>SUM(J7:M7)</f>
         <v>39800</v>
       </c>
-      <c r="CM7" s="39">
+      <c r="CR7" s="39">
         <f t="shared" si="1"/>
         <v>36200</v>
       </c>
-      <c r="CN7" s="39">
+      <c r="CS7" s="39">
         <f>SUM(R7:U7)</f>
         <v>32300</v>
       </c>
-      <c r="CO7" s="34">
+      <c r="CT7" s="34">
         <f>SUM(V7:Y7)</f>
         <v>32300</v>
       </c>
-      <c r="CP7" s="34"/>
-      <c r="CQ7" s="34"/>
-    </row>
-    <row r="8" spans="1:118" x14ac:dyDescent="0.2">
+      <c r="CU7" s="34"/>
+      <c r="CV7" s="34"/>
+    </row>
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>114</v>
       </c>
@@ -6199,26 +6289,31 @@
       <c r="CI8" s="39"/>
       <c r="CJ8" s="39"/>
       <c r="CK8" s="39"/>
-      <c r="CL8" s="39">
+      <c r="CL8" s="39"/>
+      <c r="CM8" s="39"/>
+      <c r="CN8" s="39"/>
+      <c r="CO8" s="39"/>
+      <c r="CP8" s="39"/>
+      <c r="CQ8" s="39">
         <f>SUM(J8:M8)</f>
         <v>2800</v>
       </c>
-      <c r="CM8" s="39">
+      <c r="CR8" s="39">
         <f t="shared" si="1"/>
         <v>3100</v>
       </c>
-      <c r="CN8" s="39">
+      <c r="CS8" s="39">
         <f>SUM(R8:U8)</f>
         <v>4200</v>
       </c>
-      <c r="CO8" s="34">
+      <c r="CT8" s="34">
         <f>SUM(V8:Y8)</f>
         <v>4200</v>
       </c>
-      <c r="CP8" s="34"/>
-      <c r="CQ8" s="34"/>
-    </row>
-    <row r="9" spans="1:118" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="CU8" s="34"/>
+      <c r="CV8" s="34"/>
+    </row>
+    <row r="9" spans="1:123" s="19" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B9" s="23" t="s">
         <v>236</v>
       </c>
@@ -6369,43 +6464,48 @@
       <c r="CI9" s="39"/>
       <c r="CJ9" s="39"/>
       <c r="CK9" s="39"/>
-      <c r="CL9" s="39">
+      <c r="CL9" s="39"/>
+      <c r="CM9" s="39"/>
+      <c r="CN9" s="39"/>
+      <c r="CO9" s="39"/>
+      <c r="CP9" s="39"/>
+      <c r="CQ9" s="39">
         <v>0</v>
       </c>
-      <c r="CM9" s="39">
+      <c r="CR9" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CN9" s="39">
+      <c r="CS9" s="39">
         <v>40000</v>
       </c>
-      <c r="CO9" s="39">
+      <c r="CT9" s="39">
         <f>SUM(V9:Y9)</f>
         <v>47900</v>
       </c>
-      <c r="CP9" s="39">
+      <c r="CU9" s="39">
         <v>60000</v>
       </c>
-      <c r="CQ9" s="39">
+      <c r="CV9" s="39">
         <v>70000</v>
       </c>
-      <c r="CR9" s="36"/>
-      <c r="CS9" s="36"/>
-      <c r="CT9" s="36"/>
-      <c r="CY9" s="62">
+      <c r="CW9" s="36"/>
+      <c r="CX9" s="36"/>
+      <c r="CY9" s="36"/>
+      <c r="DD9" s="62">
         <f>SUM(BR9:BU9)</f>
         <v>50700</v>
       </c>
-      <c r="CZ9" s="62">
+      <c r="DE9" s="62">
         <f>SUM(BV9:BY9)</f>
         <v>69400</v>
       </c>
-      <c r="DA9" s="62">
+      <c r="DF9" s="62">
         <f>SUM(BZ9:CC9)</f>
         <v>45300</v>
       </c>
     </row>
-    <row r="10" spans="1:118" s="55" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:123" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="55" t="s">
         <v>87</v>
       </c>
@@ -6570,38 +6670,43 @@
       <c r="CI10" s="66"/>
       <c r="CJ10" s="66"/>
       <c r="CK10" s="66"/>
-      <c r="CL10" s="66">
+      <c r="CL10" s="66"/>
+      <c r="CM10" s="66"/>
+      <c r="CN10" s="66"/>
+      <c r="CO10" s="66"/>
+      <c r="CP10" s="66"/>
+      <c r="CQ10" s="66">
         <f>SUM(J10:M10)</f>
         <v>271300</v>
       </c>
-      <c r="CM10" s="66">
+      <c r="CR10" s="66">
         <f t="shared" si="1"/>
         <v>218100</v>
       </c>
-      <c r="CN10" s="66">
-        <f>SUM(CN11:CN14)</f>
+      <c r="CS10" s="66">
+        <f>SUM(CS11:CS14)</f>
         <v>128190</v>
       </c>
-      <c r="CO10" s="66">
-        <f>SUM(CO11:CO14)</f>
+      <c r="CT10" s="66">
+        <f>SUM(CT11:CT14)</f>
         <v>85461.9140625</v>
       </c>
-      <c r="CP10" s="66">
-        <f>CO10*0.5</f>
+      <c r="CU10" s="66">
+        <f>CT10*0.5</f>
         <v>42730.95703125</v>
       </c>
-      <c r="CQ10" s="66">
-        <f>CP10*0.5</f>
+      <c r="CV10" s="66">
+        <f>CU10*0.5</f>
         <v>21365.478515625</v>
       </c>
-      <c r="CR10" s="53"/>
-      <c r="CS10" s="53"/>
-      <c r="CT10" s="53"/>
-      <c r="CY10" s="62"/>
-      <c r="CZ10" s="62"/>
-      <c r="DA10" s="62"/>
-    </row>
-    <row r="11" spans="1:118" x14ac:dyDescent="0.2">
+      <c r="CW10" s="53"/>
+      <c r="CX10" s="53"/>
+      <c r="CY10" s="53"/>
+      <c r="DD10" s="62"/>
+      <c r="DE10" s="62"/>
+      <c r="DF10" s="62"/>
+    </row>
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>110</v>
       </c>
@@ -6741,21 +6846,26 @@
       <c r="CK11" s="34"/>
       <c r="CL11" s="34"/>
       <c r="CM11" s="34"/>
-      <c r="CN11" s="34">
+      <c r="CN11" s="34"/>
+      <c r="CO11" s="34"/>
+      <c r="CP11" s="34"/>
+      <c r="CQ11" s="34"/>
+      <c r="CR11" s="34"/>
+      <c r="CS11" s="34">
         <f>SUM(R11:U11)</f>
         <v>68730</v>
       </c>
-      <c r="CO11" s="34">
+      <c r="CT11" s="34">
         <f>SUM(V11:Y11)</f>
         <v>68730</v>
       </c>
-      <c r="CP11" s="34"/>
-      <c r="CQ11" s="34"/>
-      <c r="CY11" s="62"/>
-      <c r="CZ11" s="62"/>
-      <c r="DA11" s="62"/>
-    </row>
-    <row r="12" spans="1:118" x14ac:dyDescent="0.2">
+      <c r="CU11" s="34"/>
+      <c r="CV11" s="34"/>
+      <c r="DD11" s="62"/>
+      <c r="DE11" s="62"/>
+      <c r="DF11" s="62"/>
+    </row>
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>112</v>
       </c>
@@ -6895,21 +7005,26 @@
       <c r="CK12" s="34"/>
       <c r="CL12" s="34"/>
       <c r="CM12" s="34"/>
-      <c r="CN12" s="34">
+      <c r="CN12" s="34"/>
+      <c r="CO12" s="34"/>
+      <c r="CP12" s="34"/>
+      <c r="CQ12" s="34"/>
+      <c r="CR12" s="34"/>
+      <c r="CS12" s="34">
         <f>SUM(R12:U12)</f>
         <v>41190</v>
       </c>
-      <c r="CO12" s="34">
+      <c r="CT12" s="34">
         <f>SUM(V12:Y12)</f>
         <v>8182.6171874999982</v>
       </c>
-      <c r="CP12" s="34"/>
-      <c r="CQ12" s="34"/>
-      <c r="CY12" s="62"/>
-      <c r="CZ12" s="62"/>
-      <c r="DA12" s="62"/>
-    </row>
-    <row r="13" spans="1:118" x14ac:dyDescent="0.2">
+      <c r="CU12" s="34"/>
+      <c r="CV12" s="34"/>
+      <c r="DD12" s="62"/>
+      <c r="DE12" s="62"/>
+      <c r="DF12" s="62"/>
+    </row>
+    <row r="13" spans="1:123" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>113</v>
       </c>
@@ -7049,21 +7164,26 @@
       <c r="CK13" s="34"/>
       <c r="CL13" s="34"/>
       <c r="CM13" s="34"/>
-      <c r="CN13" s="34">
+      <c r="CN13" s="34"/>
+      <c r="CO13" s="34"/>
+      <c r="CP13" s="34"/>
+      <c r="CQ13" s="34"/>
+      <c r="CR13" s="34"/>
+      <c r="CS13" s="34">
         <f>SUM(R13:U13)</f>
         <v>14940</v>
       </c>
-      <c r="CO13" s="34">
+      <c r="CT13" s="34">
         <f>SUM(V13:Y13)</f>
         <v>6029.296875</v>
       </c>
-      <c r="CP13" s="34"/>
-      <c r="CQ13" s="34"/>
-      <c r="CY13" s="62"/>
-      <c r="CZ13" s="62"/>
-      <c r="DA13" s="62"/>
-    </row>
-    <row r="14" spans="1:118" x14ac:dyDescent="0.2">
+      <c r="CU13" s="34"/>
+      <c r="CV13" s="34"/>
+      <c r="DD13" s="62"/>
+      <c r="DE13" s="62"/>
+      <c r="DF13" s="62"/>
+    </row>
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>114</v>
       </c>
@@ -7203,21 +7323,26 @@
       <c r="CK14" s="34"/>
       <c r="CL14" s="34"/>
       <c r="CM14" s="34"/>
-      <c r="CN14" s="34">
+      <c r="CN14" s="34"/>
+      <c r="CO14" s="34"/>
+      <c r="CP14" s="34"/>
+      <c r="CQ14" s="34"/>
+      <c r="CR14" s="34"/>
+      <c r="CS14" s="34">
         <f>SUM(R14:U14)</f>
         <v>3330</v>
       </c>
-      <c r="CO14" s="34">
+      <c r="CT14" s="34">
         <f>SUM(V14:Y14)</f>
         <v>2520</v>
       </c>
-      <c r="CP14" s="34"/>
-      <c r="CQ14" s="34"/>
-      <c r="CY14" s="62"/>
-      <c r="CZ14" s="62"/>
-      <c r="DA14" s="62"/>
-    </row>
-    <row r="15" spans="1:118" s="55" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="CU14" s="34"/>
+      <c r="CV14" s="34"/>
+      <c r="DD14" s="62"/>
+      <c r="DE14" s="62"/>
+      <c r="DF14" s="62"/>
+    </row>
+    <row r="15" spans="1:123" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="55" t="s">
         <v>17</v>
       </c>
@@ -7385,38 +7510,43 @@
       <c r="CI15" s="66"/>
       <c r="CJ15" s="66"/>
       <c r="CK15" s="66"/>
-      <c r="CL15" s="66">
+      <c r="CL15" s="66"/>
+      <c r="CM15" s="66"/>
+      <c r="CN15" s="66"/>
+      <c r="CO15" s="66"/>
+      <c r="CP15" s="66"/>
+      <c r="CQ15" s="66">
         <f>SUM(J15:M15)</f>
         <v>230400</v>
       </c>
-      <c r="CM15" s="66">
+      <c r="CR15" s="66">
         <f>SUM(N15:Q15)</f>
         <v>222000</v>
       </c>
-      <c r="CN15" s="66">
-        <f>CN16+CN17</f>
+      <c r="CS15" s="66">
+        <f>CS16+CS17</f>
         <v>206910</v>
       </c>
-      <c r="CO15" s="66">
-        <f>CO16+CO17</f>
+      <c r="CT15" s="66">
+        <f>CT16+CT17</f>
         <v>114142.40100000001</v>
       </c>
-      <c r="CP15" s="66">
-        <f>CO15*0.5</f>
+      <c r="CU15" s="66">
+        <f>CT15*0.5</f>
         <v>57071.200500000006</v>
       </c>
-      <c r="CQ15" s="66">
-        <f>CP15*0.5</f>
+      <c r="CV15" s="66">
+        <f>CU15*0.5</f>
         <v>28535.600250000003</v>
       </c>
-      <c r="CR15" s="53"/>
-      <c r="CS15" s="53"/>
-      <c r="CT15" s="53"/>
-      <c r="CY15" s="62"/>
-      <c r="CZ15" s="62"/>
-      <c r="DA15" s="62"/>
-    </row>
-    <row r="16" spans="1:118" x14ac:dyDescent="0.2">
+      <c r="CW15" s="53"/>
+      <c r="CX15" s="53"/>
+      <c r="CY15" s="53"/>
+      <c r="DD15" s="62"/>
+      <c r="DE15" s="62"/>
+      <c r="DF15" s="62"/>
+    </row>
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>110</v>
       </c>
@@ -7556,21 +7686,26 @@
       <c r="CK16" s="34"/>
       <c r="CL16" s="34"/>
       <c r="CM16" s="34"/>
-      <c r="CN16" s="34">
+      <c r="CN16" s="34"/>
+      <c r="CO16" s="34"/>
+      <c r="CP16" s="34"/>
+      <c r="CQ16" s="34"/>
+      <c r="CR16" s="34"/>
+      <c r="CS16" s="34">
         <f>SUM(R16:U16)</f>
         <v>133030</v>
       </c>
-      <c r="CO16" s="34">
+      <c r="CT16" s="34">
         <f>SUM(V16:Y16)</f>
         <v>79946.433000000005</v>
       </c>
-      <c r="CP16" s="34"/>
-      <c r="CQ16" s="34"/>
-      <c r="CY16" s="62"/>
-      <c r="CZ16" s="62"/>
-      <c r="DA16" s="62"/>
-    </row>
-    <row r="17" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="CU16" s="34"/>
+      <c r="CV16" s="34"/>
+      <c r="DD16" s="62"/>
+      <c r="DE16" s="62"/>
+      <c r="DF16" s="62"/>
+    </row>
+    <row r="17" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>112</v>
       </c>
@@ -7710,21 +7845,26 @@
       <c r="CK17" s="34"/>
       <c r="CL17" s="34"/>
       <c r="CM17" s="34"/>
-      <c r="CN17" s="34">
+      <c r="CN17" s="34"/>
+      <c r="CO17" s="34"/>
+      <c r="CP17" s="34"/>
+      <c r="CQ17" s="34"/>
+      <c r="CR17" s="34"/>
+      <c r="CS17" s="34">
         <f>SUM(R17:U17)</f>
         <v>73880</v>
       </c>
-      <c r="CO17" s="34">
+      <c r="CT17" s="34">
         <f>SUM(V17:Y17)</f>
         <v>34195.968000000008</v>
       </c>
-      <c r="CP17" s="34"/>
-      <c r="CQ17" s="34"/>
-      <c r="CY17" s="62"/>
-      <c r="CZ17" s="62"/>
-      <c r="DA17" s="62"/>
-    </row>
-    <row r="18" spans="2:105" s="55" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="CU17" s="34"/>
+      <c r="CV17" s="34"/>
+      <c r="DD17" s="62"/>
+      <c r="DE17" s="62"/>
+      <c r="DF17" s="62"/>
+    </row>
+    <row r="18" spans="2:110" s="55" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="55" t="s">
         <v>18</v>
       </c>
@@ -7890,40 +8030,45 @@
       <c r="CI18" s="66"/>
       <c r="CJ18" s="66"/>
       <c r="CK18" s="66"/>
-      <c r="CL18" s="66">
+      <c r="CL18" s="66"/>
+      <c r="CM18" s="66"/>
+      <c r="CN18" s="66"/>
+      <c r="CO18" s="66"/>
+      <c r="CP18" s="66"/>
+      <c r="CQ18" s="66">
         <f>SUM(J18:M18)</f>
         <v>387000</v>
       </c>
-      <c r="CM18" s="66">
+      <c r="CR18" s="66">
         <f>SUM(N18:Q18)</f>
         <v>384700</v>
       </c>
-      <c r="CN18" s="66">
-        <f>SUM(CN19:CN22)</f>
+      <c r="CS18" s="66">
+        <f>SUM(CS19:CS22)</f>
         <v>381902</v>
       </c>
-      <c r="CO18" s="66">
-        <f>SUM(CO19:CO22)</f>
+      <c r="CT18" s="66">
+        <f>SUM(CT19:CT22)</f>
         <v>335413.00575072004</v>
       </c>
-      <c r="CP18" s="66">
-        <f>CO18*0.5</f>
+      <c r="CU18" s="66">
+        <f>CT18*0.5</f>
         <v>167706.50287536002</v>
       </c>
-      <c r="CQ18" s="66">
-        <f>CP18*0.5</f>
+      <c r="CV18" s="66">
+        <f>CU18*0.5</f>
         <v>83853.25143768001</v>
       </c>
-      <c r="CR18" s="53">
+      <c r="CW18" s="53">
         <v>0</v>
       </c>
-      <c r="CS18" s="53"/>
-      <c r="CT18" s="53"/>
-      <c r="CY18" s="62"/>
-      <c r="CZ18" s="62"/>
-      <c r="DA18" s="62"/>
-    </row>
-    <row r="19" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="CX18" s="53"/>
+      <c r="CY18" s="53"/>
+      <c r="DD18" s="62"/>
+      <c r="DE18" s="62"/>
+      <c r="DF18" s="62"/>
+    </row>
+    <row r="19" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>110</v>
       </c>
@@ -8062,31 +8207,36 @@
       <c r="CJ19" s="34"/>
       <c r="CK19" s="34"/>
       <c r="CL19" s="34"/>
-      <c r="CM19" s="39">
+      <c r="CM19" s="34"/>
+      <c r="CN19" s="34"/>
+      <c r="CO19" s="34"/>
+      <c r="CP19" s="34"/>
+      <c r="CQ19" s="34"/>
+      <c r="CR19" s="39">
         <f>SUM(N19:Q19)</f>
         <v>52700</v>
       </c>
-      <c r="CN19" s="39">
+      <c r="CS19" s="39">
         <f>SUM(R19:U19)</f>
         <v>47220</v>
       </c>
-      <c r="CO19" s="34">
+      <c r="CT19" s="34">
         <f>SUM(V19:Y19)</f>
         <v>38880</v>
       </c>
-      <c r="CP19" s="34">
-        <f>CO19*0.9</f>
+      <c r="CU19" s="34">
+        <f>CT19*0.9</f>
         <v>34992</v>
       </c>
-      <c r="CQ19" s="34">
-        <f>CP19*0.9</f>
+      <c r="CV19" s="34">
+        <f>CU19*0.9</f>
         <v>31492.799999999999</v>
       </c>
-      <c r="CY19" s="62"/>
-      <c r="CZ19" s="62"/>
-      <c r="DA19" s="62"/>
-    </row>
-    <row r="20" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD19" s="62"/>
+      <c r="DE19" s="62"/>
+      <c r="DF19" s="62"/>
+    </row>
+    <row r="20" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>112</v>
       </c>
@@ -8225,31 +8375,36 @@
       <c r="CJ20" s="34"/>
       <c r="CK20" s="34"/>
       <c r="CL20" s="34"/>
-      <c r="CM20" s="39">
+      <c r="CM20" s="34"/>
+      <c r="CN20" s="34"/>
+      <c r="CO20" s="34"/>
+      <c r="CP20" s="34"/>
+      <c r="CQ20" s="34"/>
+      <c r="CR20" s="39">
         <f>SUM(N20:Q20)</f>
         <v>297000</v>
       </c>
-      <c r="CN20" s="39">
+      <c r="CS20" s="39">
         <f>SUM(R20:U20)</f>
         <v>301042</v>
       </c>
-      <c r="CO20" s="34">
+      <c r="CT20" s="34">
         <f>SUM(V20:Y20)</f>
         <v>271762.52175072004</v>
       </c>
-      <c r="CP20" s="34">
-        <f>0.5*CO20</f>
+      <c r="CU20" s="34">
+        <f>0.5*CT20</f>
         <v>135881.26087536002</v>
       </c>
-      <c r="CQ20" s="34">
-        <f>CP20*0.25</f>
+      <c r="CV20" s="34">
+        <f>CU20*0.25</f>
         <v>33970.315218840005</v>
       </c>
-      <c r="CY20" s="62"/>
-      <c r="CZ20" s="62"/>
-      <c r="DA20" s="62"/>
-    </row>
-    <row r="21" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD20" s="62"/>
+      <c r="DE20" s="62"/>
+      <c r="DF20" s="62"/>
+    </row>
+    <row r="21" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>113</v>
       </c>
@@ -8388,31 +8543,36 @@
       <c r="CJ21" s="34"/>
       <c r="CK21" s="34"/>
       <c r="CL21" s="34"/>
-      <c r="CM21" s="39">
+      <c r="CM21" s="34"/>
+      <c r="CN21" s="34"/>
+      <c r="CO21" s="34"/>
+      <c r="CP21" s="34"/>
+      <c r="CQ21" s="34"/>
+      <c r="CR21" s="39">
         <f>SUM(N21:Q21)</f>
         <v>31200</v>
       </c>
-      <c r="CN21" s="39">
+      <c r="CS21" s="39">
         <f>SUM(R21:U21)</f>
         <v>29340</v>
       </c>
-      <c r="CO21" s="34">
+      <c r="CT21" s="34">
         <f>SUM(V21:Y21)</f>
         <v>21170.484000000004</v>
       </c>
-      <c r="CP21" s="34">
-        <f>CO21*0.75</f>
+      <c r="CU21" s="34">
+        <f>CT21*0.75</f>
         <v>15877.863000000003</v>
       </c>
-      <c r="CQ21" s="34">
-        <f>CP21*0.5</f>
+      <c r="CV21" s="34">
+        <f>CU21*0.5</f>
         <v>7938.9315000000015</v>
       </c>
-      <c r="CY21" s="62"/>
-      <c r="CZ21" s="62"/>
-      <c r="DA21" s="62"/>
-    </row>
-    <row r="22" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD21" s="62"/>
+      <c r="DE21" s="62"/>
+      <c r="DF21" s="62"/>
+    </row>
+    <row r="22" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>114</v>
       </c>
@@ -8552,27 +8712,32 @@
       <c r="CK22" s="34"/>
       <c r="CL22" s="34"/>
       <c r="CM22" s="34"/>
-      <c r="CN22" s="39">
+      <c r="CN22" s="34"/>
+      <c r="CO22" s="34"/>
+      <c r="CP22" s="34"/>
+      <c r="CQ22" s="34"/>
+      <c r="CR22" s="34"/>
+      <c r="CS22" s="39">
         <f>SUM(R22:U22)</f>
         <v>4300</v>
       </c>
-      <c r="CO22" s="34">
+      <c r="CT22" s="34">
         <f>SUM(V22:Y22)</f>
         <v>3600</v>
       </c>
-      <c r="CP22" s="34">
-        <f>CO22</f>
+      <c r="CU22" s="34">
+        <f>CT22</f>
         <v>3600</v>
       </c>
-      <c r="CQ22" s="34">
-        <f>CP22*0.75</f>
+      <c r="CV22" s="34">
+        <f>CU22*0.75</f>
         <v>2700</v>
       </c>
-      <c r="CY22" s="62"/>
-      <c r="CZ22" s="62"/>
-      <c r="DA22" s="62"/>
-    </row>
-    <row r="23" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD22" s="62"/>
+      <c r="DE22" s="62"/>
+      <c r="DF22" s="62"/>
+    </row>
+    <row r="23" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>202</v>
       </c>
@@ -8700,43 +8865,48 @@
       <c r="CI23" s="34"/>
       <c r="CJ23" s="34"/>
       <c r="CK23" s="34"/>
-      <c r="CL23" s="34">
+      <c r="CL23" s="34"/>
+      <c r="CM23" s="34"/>
+      <c r="CN23" s="34"/>
+      <c r="CO23" s="34"/>
+      <c r="CP23" s="34"/>
+      <c r="CQ23" s="34">
         <v>46200</v>
       </c>
-      <c r="CM23" s="39">
-        <f t="shared" ref="CM23:CM39" si="10">SUM(R23:U23)</f>
+      <c r="CR23" s="39">
+        <f t="shared" ref="CR23:CR39" si="10">SUM(R23:U23)</f>
         <v>50800</v>
       </c>
-      <c r="CN23" s="34">
-        <f>CM23</f>
+      <c r="CS23" s="34">
+        <f>CR23</f>
         <v>50800</v>
       </c>
-      <c r="CO23" s="34">
-        <f>CN23</f>
+      <c r="CT23" s="34">
+        <f>CS23</f>
         <v>50800</v>
       </c>
-      <c r="CP23" s="34">
-        <f>CO23</f>
+      <c r="CU23" s="34">
+        <f>CT23</f>
         <v>50800</v>
       </c>
-      <c r="CQ23" s="34">
-        <f>CP23</f>
+      <c r="CV23" s="34">
+        <f>CU23</f>
         <v>50800</v>
       </c>
-      <c r="CY23" s="62">
+      <c r="DD23" s="62">
         <f>SUM(BR23:BU23)</f>
         <v>110000</v>
       </c>
-      <c r="CZ23" s="62">
+      <c r="DE23" s="62">
         <f>SUM(BV23:BY23)</f>
         <v>27700</v>
       </c>
-      <c r="DA23" s="62">
+      <c r="DF23" s="62">
         <f>SUM(BZ23:CC23)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
@@ -8879,35 +9049,40 @@
       <c r="CI24" s="34"/>
       <c r="CJ24" s="34"/>
       <c r="CK24" s="34"/>
-      <c r="CL24" s="34">
+      <c r="CL24" s="34"/>
+      <c r="CM24" s="34"/>
+      <c r="CN24" s="34"/>
+      <c r="CO24" s="34"/>
+      <c r="CP24" s="34"/>
+      <c r="CQ24" s="34">
         <f>AW24*1.03</f>
         <v>148655.78</v>
       </c>
-      <c r="CM24" s="39">
+      <c r="CR24" s="39">
         <f t="shared" si="10"/>
         <v>84700</v>
       </c>
-      <c r="CN24" s="34">
-        <f>CM24*1.03</f>
+      <c r="CS24" s="34">
+        <f>CR24*1.03</f>
         <v>87241</v>
       </c>
-      <c r="CO24" s="34">
-        <f>CN24*1.03</f>
+      <c r="CT24" s="34">
+        <f>CS24*1.03</f>
         <v>89858.23</v>
       </c>
-      <c r="CP24" s="34">
-        <f>CO24*1.03</f>
+      <c r="CU24" s="34">
+        <f>CT24*1.03</f>
         <v>92553.976899999994</v>
       </c>
-      <c r="CQ24" s="34">
-        <f>CP24*1.03</f>
+      <c r="CV24" s="34">
+        <f>CU24*1.03</f>
         <v>95330.596206999995</v>
       </c>
-      <c r="CY24" s="62"/>
-      <c r="CZ24" s="62"/>
-      <c r="DA24" s="62"/>
-    </row>
-    <row r="25" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD24" s="62"/>
+      <c r="DE24" s="62"/>
+      <c r="DF24" s="62"/>
+    </row>
+    <row r="25" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>74</v>
       </c>
@@ -9001,15 +9176,20 @@
       <c r="CI25" s="34"/>
       <c r="CJ25" s="34"/>
       <c r="CK25" s="34"/>
-      <c r="CM25" s="39">
+      <c r="CL25" s="34"/>
+      <c r="CM25" s="34"/>
+      <c r="CN25" s="34"/>
+      <c r="CO25" s="34"/>
+      <c r="CP25" s="34"/>
+      <c r="CR25" s="39">
         <f t="shared" si="10"/>
         <v>9800</v>
       </c>
-      <c r="CY25" s="62"/>
-      <c r="CZ25" s="62"/>
-      <c r="DA25" s="62"/>
-    </row>
-    <row r="26" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD25" s="62"/>
+      <c r="DE25" s="62"/>
+      <c r="DF25" s="62"/>
+    </row>
+    <row r="26" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>75</v>
       </c>
@@ -9114,24 +9294,29 @@
       <c r="CI26" s="34"/>
       <c r="CJ26" s="34"/>
       <c r="CK26" s="34"/>
-      <c r="CM26" s="39">
+      <c r="CL26" s="34"/>
+      <c r="CM26" s="34"/>
+      <c r="CN26" s="34"/>
+      <c r="CO26" s="34"/>
+      <c r="CP26" s="34"/>
+      <c r="CR26" s="39">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CY26" s="62">
-        <f t="shared" ref="CY26" si="11">SUM(BR26:BU26)</f>
+      <c r="DD26" s="62">
+        <f t="shared" ref="DD26" si="11">SUM(BR26:BU26)</f>
         <v>11600</v>
       </c>
-      <c r="CZ26" s="62">
-        <f t="shared" ref="CZ26" si="12">SUM(BV26:BY26)</f>
+      <c r="DE26" s="62">
+        <f t="shared" ref="DE26" si="12">SUM(BV26:BY26)</f>
         <v>8700</v>
       </c>
-      <c r="DA26" s="62">
-        <f t="shared" ref="DA26" si="13">SUM(BZ26:CC26)</f>
+      <c r="DF26" s="62">
+        <f t="shared" ref="DF26" si="13">SUM(BZ26:CC26)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>76</v>
       </c>
@@ -9221,31 +9406,31 @@
       <c r="AL27" s="34"/>
       <c r="AM27" s="34"/>
       <c r="AN27" s="34"/>
-      <c r="CM27" s="39">
+      <c r="CR27" s="39">
         <f t="shared" si="10"/>
         <v>33090</v>
       </c>
-      <c r="CN27" s="34">
-        <f>CM27</f>
+      <c r="CS27" s="34">
+        <f>CR27</f>
         <v>33090</v>
       </c>
-      <c r="CO27" s="34">
-        <f>CN27</f>
+      <c r="CT27" s="34">
+        <f>CS27</f>
         <v>33090</v>
       </c>
-      <c r="CP27" s="34">
-        <f>CO27</f>
+      <c r="CU27" s="34">
+        <f>CT27</f>
         <v>33090</v>
       </c>
-      <c r="CQ27" s="34">
-        <f>CP27</f>
+      <c r="CV27" s="34">
+        <f>CU27</f>
         <v>33090</v>
       </c>
-      <c r="CY27" s="62"/>
-      <c r="CZ27" s="62"/>
-      <c r="DA27" s="62"/>
-    </row>
-    <row r="28" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD27" s="62"/>
+      <c r="DE27" s="62"/>
+      <c r="DF27" s="62"/>
+    </row>
+    <row r="28" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>248</v>
       </c>
@@ -9329,31 +9514,31 @@
       <c r="AL28" s="34"/>
       <c r="AM28" s="34"/>
       <c r="AN28" s="34"/>
-      <c r="CM28" s="39">
+      <c r="CR28" s="39">
         <f t="shared" si="10"/>
         <v>36520</v>
       </c>
-      <c r="CN28" s="34">
-        <f t="shared" ref="CN28:CQ39" si="16">CM28</f>
+      <c r="CS28" s="34">
+        <f t="shared" ref="CS28:CV39" si="16">CR28</f>
         <v>36520</v>
       </c>
-      <c r="CO28" s="34">
+      <c r="CT28" s="34">
         <f t="shared" si="16"/>
         <v>36520</v>
       </c>
-      <c r="CP28" s="34">
+      <c r="CU28" s="34">
         <f t="shared" si="16"/>
         <v>36520</v>
       </c>
-      <c r="CQ28" s="34">
+      <c r="CV28" s="34">
         <f t="shared" si="16"/>
         <v>36520</v>
       </c>
-      <c r="CY28" s="62"/>
-      <c r="CZ28" s="62"/>
-      <c r="DA28" s="62"/>
-    </row>
-    <row r="29" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD28" s="62"/>
+      <c r="DE28" s="62"/>
+      <c r="DF28" s="62"/>
+    </row>
+    <row r="29" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>90</v>
       </c>
@@ -9437,31 +9622,31 @@
       <c r="AL29" s="34"/>
       <c r="AM29" s="34"/>
       <c r="AN29" s="34"/>
-      <c r="CM29" s="39">
+      <c r="CR29" s="39">
         <f t="shared" si="10"/>
         <v>17310</v>
       </c>
-      <c r="CN29" s="34">
+      <c r="CS29" s="34">
         <f t="shared" si="16"/>
         <v>17310</v>
       </c>
-      <c r="CO29" s="34">
+      <c r="CT29" s="34">
         <f t="shared" si="16"/>
         <v>17310</v>
       </c>
-      <c r="CP29" s="34">
+      <c r="CU29" s="34">
         <f t="shared" si="16"/>
         <v>17310</v>
       </c>
-      <c r="CQ29" s="34">
+      <c r="CV29" s="34">
         <f t="shared" si="16"/>
         <v>17310</v>
       </c>
-      <c r="CY29" s="62"/>
-      <c r="CZ29" s="62"/>
-      <c r="DA29" s="62"/>
-    </row>
-    <row r="30" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD29" s="62"/>
+      <c r="DE29" s="62"/>
+      <c r="DF29" s="62"/>
+    </row>
+    <row r="30" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B30" s="23" t="s">
         <v>186</v>
       </c>
@@ -9543,31 +9728,31 @@
       <c r="AL30" s="34"/>
       <c r="AM30" s="34"/>
       <c r="AN30" s="34"/>
-      <c r="CM30" s="39">
+      <c r="CR30" s="39">
         <f t="shared" si="10"/>
         <v>8170</v>
       </c>
-      <c r="CN30" s="34">
+      <c r="CS30" s="34">
         <f t="shared" si="16"/>
         <v>8170</v>
       </c>
-      <c r="CO30" s="34">
+      <c r="CT30" s="34">
         <f t="shared" si="16"/>
         <v>8170</v>
       </c>
-      <c r="CP30" s="34">
+      <c r="CU30" s="34">
         <f t="shared" si="16"/>
         <v>8170</v>
       </c>
-      <c r="CQ30" s="34">
+      <c r="CV30" s="34">
         <f t="shared" si="16"/>
         <v>8170</v>
       </c>
-      <c r="CY30" s="62"/>
-      <c r="CZ30" s="62"/>
-      <c r="DA30" s="62"/>
-    </row>
-    <row r="31" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD30" s="62"/>
+      <c r="DE30" s="62"/>
+      <c r="DF30" s="62"/>
+    </row>
+    <row r="31" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>115</v>
       </c>
@@ -9615,31 +9800,31 @@
       <c r="AL31" s="34"/>
       <c r="AM31" s="34"/>
       <c r="AN31" s="34"/>
-      <c r="CM31" s="39">
+      <c r="CR31" s="39">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CN31" s="34">
+      <c r="CS31" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="CO31" s="34">
+      <c r="CT31" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="CP31" s="34">
+      <c r="CU31" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="CQ31" s="34">
+      <c r="CV31" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="CY31" s="62"/>
-      <c r="CZ31" s="62"/>
-      <c r="DA31" s="62"/>
-    </row>
-    <row r="32" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD31" s="62"/>
+      <c r="DE31" s="62"/>
+      <c r="DF31" s="62"/>
+    </row>
+    <row r="32" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B32" s="23" t="s">
         <v>203</v>
       </c>
@@ -9685,31 +9870,31 @@
       <c r="AL32" s="34"/>
       <c r="AM32" s="34"/>
       <c r="AN32" s="34"/>
-      <c r="CM32" s="39">
+      <c r="CR32" s="39">
         <f t="shared" si="10"/>
         <v>8800</v>
       </c>
-      <c r="CN32" s="34">
+      <c r="CS32" s="34">
         <f t="shared" si="16"/>
         <v>8800</v>
       </c>
-      <c r="CO32" s="34">
+      <c r="CT32" s="34">
         <f t="shared" si="16"/>
         <v>8800</v>
       </c>
-      <c r="CP32" s="34">
+      <c r="CU32" s="34">
         <f t="shared" si="16"/>
         <v>8800</v>
       </c>
-      <c r="CQ32" s="34">
+      <c r="CV32" s="34">
         <f t="shared" si="16"/>
         <v>8800</v>
       </c>
-      <c r="CY32" s="62"/>
-      <c r="CZ32" s="62"/>
-      <c r="DA32" s="62"/>
-    </row>
-    <row r="33" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD32" s="62"/>
+      <c r="DE32" s="62"/>
+      <c r="DF32" s="62"/>
+    </row>
+    <row r="33" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B33" s="23" t="s">
         <v>145</v>
       </c>
@@ -9791,31 +9976,31 @@
       <c r="AL33" s="34"/>
       <c r="AM33" s="34"/>
       <c r="AN33" s="34"/>
-      <c r="CM33" s="39">
+      <c r="CR33" s="39">
         <f t="shared" si="10"/>
         <v>10190</v>
       </c>
-      <c r="CN33" s="34">
+      <c r="CS33" s="34">
         <f t="shared" si="16"/>
         <v>10190</v>
       </c>
-      <c r="CO33" s="34">
+      <c r="CT33" s="34">
         <f t="shared" si="16"/>
         <v>10190</v>
       </c>
-      <c r="CP33" s="34">
+      <c r="CU33" s="34">
         <f t="shared" si="16"/>
         <v>10190</v>
       </c>
-      <c r="CQ33" s="34">
+      <c r="CV33" s="34">
         <f t="shared" si="16"/>
         <v>10190</v>
       </c>
-      <c r="CY33" s="62"/>
-      <c r="CZ33" s="62"/>
-      <c r="DA33" s="62"/>
-    </row>
-    <row r="34" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD33" s="62"/>
+      <c r="DE33" s="62"/>
+      <c r="DF33" s="62"/>
+    </row>
+    <row r="34" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>116</v>
       </c>
@@ -9899,31 +10084,31 @@
       <c r="AL34" s="34"/>
       <c r="AM34" s="34"/>
       <c r="AN34" s="34"/>
-      <c r="CM34" s="39">
+      <c r="CR34" s="39">
         <f t="shared" si="10"/>
         <v>8600</v>
       </c>
-      <c r="CN34" s="34">
+      <c r="CS34" s="34">
         <f t="shared" si="16"/>
         <v>8600</v>
       </c>
-      <c r="CO34" s="34">
+      <c r="CT34" s="34">
         <f t="shared" si="16"/>
         <v>8600</v>
       </c>
-      <c r="CP34" s="34">
+      <c r="CU34" s="34">
         <f t="shared" si="16"/>
         <v>8600</v>
       </c>
-      <c r="CQ34" s="34">
+      <c r="CV34" s="34">
         <f t="shared" si="16"/>
         <v>8600</v>
       </c>
-      <c r="CY34" s="62"/>
-      <c r="CZ34" s="62"/>
-      <c r="DA34" s="62"/>
-    </row>
-    <row r="35" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD34" s="62"/>
+      <c r="DE34" s="62"/>
+      <c r="DF34" s="62"/>
+    </row>
+    <row r="35" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>117</v>
       </c>
@@ -9985,31 +10170,31 @@
       <c r="AL35" s="34"/>
       <c r="AM35" s="34"/>
       <c r="AN35" s="34"/>
-      <c r="CM35" s="39">
+      <c r="CR35" s="39">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="CN35" s="34">
+      <c r="CS35" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="CO35" s="34">
+      <c r="CT35" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="CP35" s="34">
+      <c r="CU35" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="CQ35" s="34">
+      <c r="CV35" s="34">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="CY35" s="62"/>
-      <c r="CZ35" s="62"/>
-      <c r="DA35" s="62"/>
-    </row>
-    <row r="36" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD35" s="62"/>
+      <c r="DE35" s="62"/>
+      <c r="DF35" s="62"/>
+    </row>
+    <row r="36" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>118</v>
       </c>
@@ -10093,31 +10278,31 @@
       <c r="AL36" s="34"/>
       <c r="AM36" s="34"/>
       <c r="AN36" s="34"/>
-      <c r="CM36" s="39">
+      <c r="CR36" s="39">
         <f t="shared" si="10"/>
         <v>8720</v>
       </c>
-      <c r="CN36" s="34">
+      <c r="CS36" s="34">
         <f t="shared" si="16"/>
         <v>8720</v>
       </c>
-      <c r="CO36" s="34">
+      <c r="CT36" s="34">
         <f t="shared" si="16"/>
         <v>8720</v>
       </c>
-      <c r="CP36" s="34">
+      <c r="CU36" s="34">
         <f t="shared" si="16"/>
         <v>8720</v>
       </c>
-      <c r="CQ36" s="34">
+      <c r="CV36" s="34">
         <f t="shared" si="16"/>
         <v>8720</v>
       </c>
-      <c r="CY36" s="62"/>
-      <c r="CZ36" s="62"/>
-      <c r="DA36" s="62"/>
-    </row>
-    <row r="37" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD36" s="62"/>
+      <c r="DE36" s="62"/>
+      <c r="DF36" s="62"/>
+    </row>
+    <row r="37" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B37" s="23" t="s">
         <v>204</v>
       </c>
@@ -10167,31 +10352,31 @@
       <c r="AL37" s="34"/>
       <c r="AM37" s="34"/>
       <c r="AN37" s="34"/>
-      <c r="CM37" s="39">
+      <c r="CR37" s="39">
         <f t="shared" si="10"/>
         <v>2400</v>
       </c>
-      <c r="CN37" s="34">
+      <c r="CS37" s="34">
         <f t="shared" si="16"/>
         <v>2400</v>
       </c>
-      <c r="CO37" s="34">
+      <c r="CT37" s="34">
         <f t="shared" si="16"/>
         <v>2400</v>
       </c>
-      <c r="CP37" s="34">
+      <c r="CU37" s="34">
         <f t="shared" si="16"/>
         <v>2400</v>
       </c>
-      <c r="CQ37" s="34">
+      <c r="CV37" s="34">
         <f t="shared" si="16"/>
         <v>2400</v>
       </c>
-      <c r="CY37" s="62"/>
-      <c r="CZ37" s="62"/>
-      <c r="DA37" s="62"/>
-    </row>
-    <row r="38" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD37" s="62"/>
+      <c r="DE37" s="62"/>
+      <c r="DF37" s="62"/>
+    </row>
+    <row r="38" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>119</v>
       </c>
@@ -10275,31 +10460,31 @@
       <c r="AL38" s="34"/>
       <c r="AM38" s="34"/>
       <c r="AN38" s="34"/>
-      <c r="CM38" s="39">
+      <c r="CR38" s="39">
         <f t="shared" si="10"/>
         <v>5850</v>
       </c>
-      <c r="CN38" s="34">
+      <c r="CS38" s="34">
         <f t="shared" si="16"/>
         <v>5850</v>
       </c>
-      <c r="CO38" s="34">
+      <c r="CT38" s="34">
         <f t="shared" si="16"/>
         <v>5850</v>
       </c>
-      <c r="CP38" s="34">
+      <c r="CU38" s="34">
         <f t="shared" si="16"/>
         <v>5850</v>
       </c>
-      <c r="CQ38" s="34">
+      <c r="CV38" s="34">
         <f t="shared" si="16"/>
         <v>5850</v>
       </c>
-      <c r="CY38" s="62"/>
-      <c r="CZ38" s="62"/>
-      <c r="DA38" s="62"/>
-    </row>
-    <row r="39" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD38" s="62"/>
+      <c r="DE38" s="62"/>
+      <c r="DF38" s="62"/>
+    </row>
+    <row r="39" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>120</v>
       </c>
@@ -10369,31 +10554,31 @@
       <c r="AL39" s="34"/>
       <c r="AM39" s="34"/>
       <c r="AN39" s="34"/>
-      <c r="CM39" s="39">
+      <c r="CR39" s="39">
         <f t="shared" si="10"/>
         <v>3600</v>
       </c>
-      <c r="CN39" s="34">
+      <c r="CS39" s="34">
         <f t="shared" si="16"/>
         <v>3600</v>
       </c>
-      <c r="CO39" s="34">
+      <c r="CT39" s="34">
         <f t="shared" si="16"/>
         <v>3600</v>
       </c>
-      <c r="CP39" s="34">
+      <c r="CU39" s="34">
         <f t="shared" si="16"/>
         <v>3600</v>
       </c>
-      <c r="CQ39" s="34">
+      <c r="CV39" s="34">
         <f t="shared" si="16"/>
         <v>3600</v>
       </c>
-      <c r="CY39" s="62"/>
-      <c r="CZ39" s="62"/>
-      <c r="DA39" s="62"/>
-    </row>
-    <row r="40" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD39" s="62"/>
+      <c r="DE39" s="62"/>
+      <c r="DF39" s="62"/>
+    </row>
+    <row r="40" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>121</v>
       </c>
@@ -10446,12 +10631,12 @@
       <c r="AL40" s="34"/>
       <c r="AM40" s="34"/>
       <c r="AN40" s="34"/>
-      <c r="CM40" s="39"/>
-      <c r="CY40" s="62"/>
-      <c r="CZ40" s="62"/>
-      <c r="DA40" s="62"/>
-    </row>
-    <row r="41" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="CR40" s="39"/>
+      <c r="DD40" s="62"/>
+      <c r="DE40" s="62"/>
+      <c r="DF40" s="62"/>
+    </row>
+    <row r="41" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B41" s="23" t="s">
         <v>205</v>
       </c>
@@ -10570,35 +10755,40 @@
       <c r="CI41" s="34"/>
       <c r="CJ41" s="34"/>
       <c r="CK41" s="34"/>
-      <c r="CL41" s="34">
+      <c r="CL41" s="34"/>
+      <c r="CM41" s="34"/>
+      <c r="CN41" s="34"/>
+      <c r="CO41" s="34"/>
+      <c r="CP41" s="34"/>
+      <c r="CQ41" s="34">
         <f>AW41*1.05</f>
         <v>420791.7</v>
       </c>
-      <c r="CM41" s="39">
+      <c r="CR41" s="39">
         <f>SUM(R41:U41)</f>
         <v>112900</v>
       </c>
-      <c r="CN41" s="34">
-        <f>CM41*1.05</f>
+      <c r="CS41" s="34">
+        <f>CR41*1.05</f>
         <v>118545</v>
       </c>
-      <c r="CO41" s="34">
-        <f>CN41*1.05</f>
+      <c r="CT41" s="34">
+        <f>CS41*1.05</f>
         <v>124472.25</v>
       </c>
-      <c r="CP41" s="34">
-        <f>CO41*1.05</f>
+      <c r="CU41" s="34">
+        <f>CT41*1.05</f>
         <v>130695.8625</v>
       </c>
-      <c r="CQ41" s="34">
-        <f>CP41*1.05</f>
+      <c r="CV41" s="34">
+        <f>CU41*1.05</f>
         <v>137230.65562500001</v>
       </c>
-      <c r="CY41" s="62"/>
-      <c r="CZ41" s="62"/>
-      <c r="DA41" s="62"/>
-    </row>
-    <row r="42" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD41" s="62"/>
+      <c r="DE41" s="62"/>
+      <c r="DF41" s="62"/>
+    </row>
+    <row r="42" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B42" s="23" t="s">
         <v>206</v>
       </c>
@@ -10706,31 +10896,36 @@
       <c r="CJ42" s="34"/>
       <c r="CK42" s="34"/>
       <c r="CL42" s="34"/>
-      <c r="CM42" s="39">
+      <c r="CM42" s="34"/>
+      <c r="CN42" s="34"/>
+      <c r="CO42" s="34"/>
+      <c r="CP42" s="34"/>
+      <c r="CQ42" s="34"/>
+      <c r="CR42" s="39">
         <f>SUM(R42:U42)</f>
         <v>33400</v>
       </c>
-      <c r="CN42" s="34">
-        <f t="shared" ref="CN42:CQ45" si="19">CM42</f>
+      <c r="CS42" s="34">
+        <f t="shared" ref="CS42:CV45" si="19">CR42</f>
         <v>33400</v>
       </c>
-      <c r="CO42" s="34">
+      <c r="CT42" s="34">
         <f t="shared" si="19"/>
         <v>33400</v>
       </c>
-      <c r="CP42" s="34">
+      <c r="CU42" s="34">
         <f t="shared" si="19"/>
         <v>33400</v>
       </c>
-      <c r="CQ42" s="34">
+      <c r="CV42" s="34">
         <f t="shared" si="19"/>
         <v>33400</v>
       </c>
-      <c r="CY42" s="62"/>
-      <c r="CZ42" s="62"/>
-      <c r="DA42" s="62"/>
-    </row>
-    <row r="43" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD42" s="62"/>
+      <c r="DE42" s="62"/>
+      <c r="DF42" s="62"/>
+    </row>
+    <row r="43" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B43" s="23" t="s">
         <v>207</v>
       </c>
@@ -10838,31 +11033,36 @@
       <c r="CJ43" s="34"/>
       <c r="CK43" s="34"/>
       <c r="CL43" s="34"/>
-      <c r="CM43" s="39">
+      <c r="CM43" s="34"/>
+      <c r="CN43" s="34"/>
+      <c r="CO43" s="34"/>
+      <c r="CP43" s="34"/>
+      <c r="CQ43" s="34"/>
+      <c r="CR43" s="39">
         <f>SUM(R43:U43)</f>
         <v>68300</v>
       </c>
-      <c r="CN43" s="34">
+      <c r="CS43" s="34">
         <f t="shared" si="19"/>
         <v>68300</v>
       </c>
-      <c r="CO43" s="34">
+      <c r="CT43" s="34">
         <f t="shared" si="19"/>
         <v>68300</v>
       </c>
-      <c r="CP43" s="34">
+      <c r="CU43" s="34">
         <f t="shared" si="19"/>
         <v>68300</v>
       </c>
-      <c r="CQ43" s="34">
+      <c r="CV43" s="34">
         <f t="shared" si="19"/>
         <v>68300</v>
       </c>
-      <c r="CY43" s="62"/>
-      <c r="CZ43" s="62"/>
-      <c r="DA43" s="62"/>
-    </row>
-    <row r="44" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD43" s="62"/>
+      <c r="DE43" s="62"/>
+      <c r="DF43" s="62"/>
+    </row>
+    <row r="44" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B44" s="23" t="s">
         <v>208</v>
       </c>
@@ -10970,31 +11170,36 @@
       <c r="CJ44" s="34"/>
       <c r="CK44" s="34"/>
       <c r="CL44" s="34"/>
-      <c r="CM44" s="39">
+      <c r="CM44" s="34"/>
+      <c r="CN44" s="34"/>
+      <c r="CO44" s="34"/>
+      <c r="CP44" s="34"/>
+      <c r="CQ44" s="34"/>
+      <c r="CR44" s="39">
         <f>SUM(R44:U44)</f>
         <v>10600</v>
       </c>
-      <c r="CN44" s="34">
+      <c r="CS44" s="34">
         <f t="shared" si="19"/>
         <v>10600</v>
       </c>
-      <c r="CO44" s="34">
+      <c r="CT44" s="34">
         <f t="shared" si="19"/>
         <v>10600</v>
       </c>
-      <c r="CP44" s="34">
+      <c r="CU44" s="34">
         <f t="shared" si="19"/>
         <v>10600</v>
       </c>
-      <c r="CQ44" s="34">
+      <c r="CV44" s="34">
         <f t="shared" si="19"/>
         <v>10600</v>
       </c>
-      <c r="CY44" s="62"/>
-      <c r="CZ44" s="62"/>
-      <c r="DA44" s="62"/>
-    </row>
-    <row r="45" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD44" s="62"/>
+      <c r="DE44" s="62"/>
+      <c r="DF44" s="62"/>
+    </row>
+    <row r="45" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B45" s="23" t="s">
         <v>209</v>
       </c>
@@ -11112,31 +11317,36 @@
       <c r="CJ45" s="34"/>
       <c r="CK45" s="34"/>
       <c r="CL45" s="34"/>
-      <c r="CM45" s="39">
+      <c r="CM45" s="34"/>
+      <c r="CN45" s="34"/>
+      <c r="CO45" s="34"/>
+      <c r="CP45" s="34"/>
+      <c r="CQ45" s="34"/>
+      <c r="CR45" s="39">
         <f>SUM(R45:U45)</f>
         <v>83510</v>
       </c>
-      <c r="CN45" s="34">
+      <c r="CS45" s="34">
         <f t="shared" si="19"/>
         <v>83510</v>
       </c>
-      <c r="CO45" s="34">
+      <c r="CT45" s="34">
         <f t="shared" si="19"/>
         <v>83510</v>
       </c>
-      <c r="CP45" s="34">
+      <c r="CU45" s="34">
         <f t="shared" si="19"/>
         <v>83510</v>
       </c>
-      <c r="CQ45" s="34">
+      <c r="CV45" s="34">
         <f t="shared" si="19"/>
         <v>83510</v>
       </c>
-      <c r="CY45" s="62"/>
-      <c r="CZ45" s="62"/>
-      <c r="DA45" s="62"/>
-    </row>
-    <row r="46" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="DD45" s="62"/>
+      <c r="DE45" s="62"/>
+      <c r="DF45" s="62"/>
+    </row>
+    <row r="46" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B46" s="23" t="s">
         <v>387</v>
       </c>
@@ -11233,25 +11443,30 @@
       <c r="CJ46" s="34"/>
       <c r="CK46" s="34"/>
       <c r="CL46" s="34"/>
-      <c r="CM46" s="39"/>
+      <c r="CM46" s="34"/>
       <c r="CN46" s="34"/>
       <c r="CO46" s="34"/>
       <c r="CP46" s="34"/>
       <c r="CQ46" s="34"/>
-      <c r="CY46" s="62">
-        <f t="shared" ref="CY46" si="20">SUM(BR46:BU46)</f>
+      <c r="CR46" s="39"/>
+      <c r="CS46" s="34"/>
+      <c r="CT46" s="34"/>
+      <c r="CU46" s="34"/>
+      <c r="CV46" s="34"/>
+      <c r="DD46" s="62">
+        <f t="shared" ref="DD46" si="20">SUM(BR46:BU46)</f>
         <v>13400</v>
       </c>
-      <c r="CZ46" s="62">
-        <f t="shared" ref="CZ46" si="21">SUM(BV46:BY46)</f>
+      <c r="DE46" s="62">
+        <f t="shared" ref="DE46" si="21">SUM(BV46:BY46)</f>
         <v>15800</v>
       </c>
-      <c r="DA46" s="62">
-        <f t="shared" ref="DA46" si="22">SUM(BZ46:CC46)</f>
+      <c r="DF46" s="62">
+        <f t="shared" ref="DF46" si="22">SUM(BZ46:CC46)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B47" s="23" t="s">
         <v>386</v>
       </c>
@@ -11364,25 +11579,30 @@
       <c r="CJ47" s="34"/>
       <c r="CK47" s="34"/>
       <c r="CL47" s="34"/>
-      <c r="CM47" s="39"/>
+      <c r="CM47" s="34"/>
       <c r="CN47" s="34"/>
       <c r="CO47" s="34"/>
       <c r="CP47" s="34"/>
       <c r="CQ47" s="34"/>
-      <c r="CY47" s="62">
-        <f t="shared" ref="CY47:CY53" si="23">SUM(BR47:BU47)</f>
+      <c r="CR47" s="39"/>
+      <c r="CS47" s="34"/>
+      <c r="CT47" s="34"/>
+      <c r="CU47" s="34"/>
+      <c r="CV47" s="34"/>
+      <c r="DD47" s="62">
+        <f t="shared" ref="DD47:DD53" si="23">SUM(BR47:BU47)</f>
         <v>13600</v>
       </c>
-      <c r="CZ47" s="62">
-        <f t="shared" ref="CZ47:CZ53" si="24">SUM(BV47:BY47)</f>
+      <c r="DE47" s="62">
+        <f t="shared" ref="DE47:DE53" si="24">SUM(BV47:BY47)</f>
         <v>13500</v>
       </c>
-      <c r="DA47" s="62">
-        <f t="shared" ref="DA47:DA53" si="25">SUM(BZ47:CC47)</f>
+      <c r="DF47" s="62">
+        <f t="shared" ref="DF47:DF53" si="25">SUM(BZ47:CC47)</f>
         <v>13600</v>
       </c>
     </row>
-    <row r="48" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B48" s="23" t="s">
         <v>385</v>
       </c>
@@ -11479,25 +11699,30 @@
       <c r="CJ48" s="34"/>
       <c r="CK48" s="34"/>
       <c r="CL48" s="34"/>
-      <c r="CM48" s="39"/>
+      <c r="CM48" s="34"/>
       <c r="CN48" s="34"/>
       <c r="CO48" s="34"/>
       <c r="CP48" s="34"/>
       <c r="CQ48" s="34"/>
-      <c r="CY48" s="62">
+      <c r="CR48" s="39"/>
+      <c r="CS48" s="34"/>
+      <c r="CT48" s="34"/>
+      <c r="CU48" s="34"/>
+      <c r="CV48" s="34"/>
+      <c r="DD48" s="62">
         <f t="shared" si="23"/>
         <v>32600</v>
       </c>
-      <c r="CZ48" s="62">
+      <c r="DE48" s="62">
         <f t="shared" si="24"/>
         <v>16700</v>
       </c>
-      <c r="DA48" s="62">
+      <c r="DF48" s="62">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B49" s="23" t="s">
         <v>384</v>
       </c>
@@ -11610,25 +11835,30 @@
       <c r="CJ49" s="34"/>
       <c r="CK49" s="34"/>
       <c r="CL49" s="34"/>
-      <c r="CM49" s="39"/>
+      <c r="CM49" s="34"/>
       <c r="CN49" s="34"/>
       <c r="CO49" s="34"/>
       <c r="CP49" s="34"/>
       <c r="CQ49" s="34"/>
-      <c r="CY49" s="62">
+      <c r="CR49" s="39"/>
+      <c r="CS49" s="34"/>
+      <c r="CT49" s="34"/>
+      <c r="CU49" s="34"/>
+      <c r="CV49" s="34"/>
+      <c r="DD49" s="62">
         <f t="shared" si="23"/>
         <v>76200</v>
       </c>
-      <c r="CZ49" s="62">
+      <c r="DE49" s="62">
         <f t="shared" si="24"/>
         <v>72900</v>
       </c>
-      <c r="DA49" s="62">
+      <c r="DF49" s="62">
         <f t="shared" si="25"/>
         <v>33700</v>
       </c>
     </row>
-    <row r="50" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B50" s="55" t="s">
         <v>463</v>
       </c>
@@ -11726,16 +11956,21 @@
       <c r="CJ50" s="34"/>
       <c r="CK50" s="34"/>
       <c r="CL50" s="34"/>
-      <c r="CM50" s="39"/>
+      <c r="CM50" s="34"/>
       <c r="CN50" s="34"/>
       <c r="CO50" s="34"/>
       <c r="CP50" s="34"/>
       <c r="CQ50" s="34"/>
-      <c r="CY50" s="62"/>
-      <c r="CZ50" s="62"/>
-      <c r="DA50" s="62"/>
-    </row>
-    <row r="51" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="CR50" s="39"/>
+      <c r="CS50" s="34"/>
+      <c r="CT50" s="34"/>
+      <c r="CU50" s="34"/>
+      <c r="CV50" s="34"/>
+      <c r="DD50" s="62"/>
+      <c r="DE50" s="62"/>
+      <c r="DF50" s="62"/>
+    </row>
+    <row r="51" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B51" s="55" t="s">
         <v>545</v>
       </c>
@@ -11833,16 +12068,21 @@
       <c r="CJ51" s="34"/>
       <c r="CK51" s="34"/>
       <c r="CL51" s="34"/>
-      <c r="CM51" s="39"/>
+      <c r="CM51" s="34"/>
       <c r="CN51" s="34"/>
       <c r="CO51" s="34"/>
       <c r="CP51" s="34"/>
       <c r="CQ51" s="34"/>
-      <c r="CY51" s="62"/>
-      <c r="CZ51" s="62"/>
-      <c r="DA51" s="62"/>
-    </row>
-    <row r="52" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="CR51" s="39"/>
+      <c r="CS51" s="34"/>
+      <c r="CT51" s="34"/>
+      <c r="CU51" s="34"/>
+      <c r="CV51" s="34"/>
+      <c r="DD51" s="62"/>
+      <c r="DE51" s="62"/>
+      <c r="DF51" s="62"/>
+    </row>
+    <row r="52" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B52" s="23" t="s">
         <v>383</v>
       </c>
@@ -11956,25 +12196,30 @@
       <c r="CJ52" s="34"/>
       <c r="CK52" s="34"/>
       <c r="CL52" s="34"/>
-      <c r="CM52" s="39"/>
+      <c r="CM52" s="34"/>
       <c r="CN52" s="34"/>
       <c r="CO52" s="34"/>
       <c r="CP52" s="34"/>
       <c r="CQ52" s="34"/>
-      <c r="CY52" s="62">
+      <c r="CR52" s="39"/>
+      <c r="CS52" s="34"/>
+      <c r="CT52" s="34"/>
+      <c r="CU52" s="34"/>
+      <c r="CV52" s="34"/>
+      <c r="DD52" s="62">
         <f t="shared" si="23"/>
         <v>21400</v>
       </c>
-      <c r="CZ52" s="62">
+      <c r="DE52" s="62">
         <f t="shared" si="24"/>
         <v>24800</v>
       </c>
-      <c r="DA52" s="62">
+      <c r="DF52" s="62">
         <f t="shared" si="25"/>
         <v>23700</v>
       </c>
     </row>
-    <row r="53" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B53" s="23" t="s">
         <v>382</v>
       </c>
@@ -12088,25 +12333,30 @@
       <c r="CJ53" s="34"/>
       <c r="CK53" s="34"/>
       <c r="CL53" s="34"/>
-      <c r="CM53" s="39"/>
+      <c r="CM53" s="34"/>
       <c r="CN53" s="34"/>
       <c r="CO53" s="34"/>
       <c r="CP53" s="34"/>
       <c r="CQ53" s="34"/>
-      <c r="CY53" s="62">
+      <c r="CR53" s="39"/>
+      <c r="CS53" s="34"/>
+      <c r="CT53" s="34"/>
+      <c r="CU53" s="34"/>
+      <c r="CV53" s="34"/>
+      <c r="DD53" s="62">
         <f t="shared" si="23"/>
         <v>20800</v>
       </c>
-      <c r="CZ53" s="62">
+      <c r="DE53" s="62">
         <f t="shared" si="24"/>
         <v>28500</v>
       </c>
-      <c r="DA53" s="62">
+      <c r="DF53" s="62">
         <f t="shared" si="25"/>
         <v>41700</v>
       </c>
     </row>
-    <row r="54" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B54" s="23" t="s">
         <v>381</v>
       </c>
@@ -12219,25 +12469,30 @@
       <c r="CJ54" s="34"/>
       <c r="CK54" s="34"/>
       <c r="CL54" s="34"/>
-      <c r="CM54" s="39"/>
+      <c r="CM54" s="34"/>
       <c r="CN54" s="34"/>
       <c r="CO54" s="34"/>
       <c r="CP54" s="34"/>
       <c r="CQ54" s="34"/>
-      <c r="CY54" s="62">
-        <f t="shared" ref="CY54:CY57" si="26">SUM(BR54:BU54)</f>
+      <c r="CR54" s="39"/>
+      <c r="CS54" s="34"/>
+      <c r="CT54" s="34"/>
+      <c r="CU54" s="34"/>
+      <c r="CV54" s="34"/>
+      <c r="DD54" s="62">
+        <f t="shared" ref="DD54:DD57" si="26">SUM(BR54:BU54)</f>
         <v>18900</v>
       </c>
-      <c r="CZ54" s="62">
-        <f t="shared" ref="CZ54:CZ57" si="27">SUM(BV54:BY54)</f>
+      <c r="DE54" s="62">
+        <f t="shared" ref="DE54:DE57" si="27">SUM(BV54:BY54)</f>
         <v>16300</v>
       </c>
-      <c r="DA54" s="62">
-        <f t="shared" ref="DA54:DA57" si="28">SUM(BZ54:CC54)</f>
+      <c r="DF54" s="62">
+        <f t="shared" ref="DF54:DF57" si="28">SUM(BZ54:CC54)</f>
         <v>33500</v>
       </c>
     </row>
-    <row r="55" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B55" s="23" t="s">
         <v>380</v>
       </c>
@@ -12357,25 +12612,30 @@
       <c r="CJ55" s="34"/>
       <c r="CK55" s="34"/>
       <c r="CL55" s="34"/>
-      <c r="CM55" s="39"/>
+      <c r="CM55" s="34"/>
       <c r="CN55" s="34"/>
       <c r="CO55" s="34"/>
       <c r="CP55" s="34"/>
       <c r="CQ55" s="34"/>
-      <c r="CY55" s="62">
+      <c r="CR55" s="39"/>
+      <c r="CS55" s="34"/>
+      <c r="CT55" s="34"/>
+      <c r="CU55" s="34"/>
+      <c r="CV55" s="34"/>
+      <c r="DD55" s="62">
         <f t="shared" si="26"/>
         <v>82400</v>
       </c>
-      <c r="CZ55" s="62">
+      <c r="DE55" s="62">
         <f t="shared" si="27"/>
         <v>100100</v>
       </c>
-      <c r="DA55" s="62">
+      <c r="DF55" s="62">
         <f t="shared" si="28"/>
         <v>104800</v>
       </c>
     </row>
-    <row r="56" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B56" s="23" t="s">
         <v>379</v>
       </c>
@@ -12494,25 +12754,30 @@
       <c r="CJ56" s="34"/>
       <c r="CK56" s="34"/>
       <c r="CL56" s="34"/>
-      <c r="CM56" s="39"/>
+      <c r="CM56" s="34"/>
       <c r="CN56" s="34"/>
       <c r="CO56" s="34"/>
       <c r="CP56" s="34"/>
       <c r="CQ56" s="34"/>
-      <c r="CY56" s="62">
+      <c r="CR56" s="39"/>
+      <c r="CS56" s="34"/>
+      <c r="CT56" s="34"/>
+      <c r="CU56" s="34"/>
+      <c r="CV56" s="34"/>
+      <c r="DD56" s="62">
         <f t="shared" si="26"/>
         <v>327100</v>
       </c>
-      <c r="CZ56" s="62">
+      <c r="DE56" s="62">
         <f t="shared" si="27"/>
         <v>459300</v>
       </c>
-      <c r="DA56" s="62">
+      <c r="DF56" s="62">
         <f t="shared" si="28"/>
         <v>423200</v>
       </c>
     </row>
-    <row r="57" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B57" s="23" t="s">
         <v>378</v>
       </c>
@@ -12625,25 +12890,30 @@
       <c r="CJ57" s="34"/>
       <c r="CK57" s="34"/>
       <c r="CL57" s="34"/>
-      <c r="CM57" s="39"/>
+      <c r="CM57" s="34"/>
       <c r="CN57" s="34"/>
       <c r="CO57" s="34"/>
       <c r="CP57" s="34"/>
       <c r="CQ57" s="34"/>
-      <c r="CY57" s="62">
+      <c r="CR57" s="39"/>
+      <c r="CS57" s="34"/>
+      <c r="CT57" s="34"/>
+      <c r="CU57" s="34"/>
+      <c r="CV57" s="34"/>
+      <c r="DD57" s="62">
         <f t="shared" si="26"/>
         <v>3300</v>
       </c>
-      <c r="CZ57" s="62">
+      <c r="DE57" s="62">
         <f t="shared" si="27"/>
         <v>4900</v>
       </c>
-      <c r="DA57" s="62">
+      <c r="DF57" s="62">
         <f t="shared" si="28"/>
         <v>16000</v>
       </c>
     </row>
-    <row r="58" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B58" s="23" t="s">
         <v>377</v>
       </c>
@@ -12740,25 +13010,30 @@
       <c r="CJ58" s="34"/>
       <c r="CK58" s="34"/>
       <c r="CL58" s="34"/>
-      <c r="CM58" s="39"/>
+      <c r="CM58" s="34"/>
       <c r="CN58" s="34"/>
       <c r="CO58" s="34"/>
       <c r="CP58" s="34"/>
       <c r="CQ58" s="34"/>
-      <c r="CY58" s="62">
-        <f t="shared" ref="CY58:CY75" si="31">SUM(BR58:BU58)</f>
+      <c r="CR58" s="39"/>
+      <c r="CS58" s="34"/>
+      <c r="CT58" s="34"/>
+      <c r="CU58" s="34"/>
+      <c r="CV58" s="34"/>
+      <c r="DD58" s="62">
+        <f t="shared" ref="DD58:DD75" si="31">SUM(BR58:BU58)</f>
         <v>900</v>
       </c>
-      <c r="CZ58" s="62">
-        <f t="shared" ref="CZ58:CZ75" si="32">SUM(BV58:BY58)</f>
+      <c r="DE58" s="62">
+        <f t="shared" ref="DE58:DE75" si="32">SUM(BV58:BY58)</f>
         <v>3700</v>
       </c>
-      <c r="DA58" s="62">
-        <f t="shared" ref="DA58:DA75" si="33">SUM(BZ58:CC58)</f>
+      <c r="DF58" s="62">
+        <f t="shared" ref="DF58:DF75" si="33">SUM(BZ58:CC58)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B59" s="23" t="s">
         <v>376</v>
       </c>
@@ -12871,25 +13146,30 @@
       <c r="CJ59" s="34"/>
       <c r="CK59" s="34"/>
       <c r="CL59" s="34"/>
-      <c r="CM59" s="39"/>
+      <c r="CM59" s="34"/>
       <c r="CN59" s="34"/>
       <c r="CO59" s="34"/>
       <c r="CP59" s="34"/>
       <c r="CQ59" s="34"/>
-      <c r="CY59" s="62">
+      <c r="CR59" s="39"/>
+      <c r="CS59" s="34"/>
+      <c r="CT59" s="34"/>
+      <c r="CU59" s="34"/>
+      <c r="CV59" s="34"/>
+      <c r="DD59" s="62">
         <f t="shared" si="31"/>
         <v>6500</v>
       </c>
-      <c r="CZ59" s="62">
+      <c r="DE59" s="62">
         <f t="shared" si="32"/>
         <v>7800</v>
       </c>
-      <c r="DA59" s="62">
+      <c r="DF59" s="62">
         <f t="shared" si="33"/>
         <v>8400</v>
       </c>
     </row>
-    <row r="60" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B60" s="23" t="s">
         <v>375</v>
       </c>
@@ -13003,25 +13283,30 @@
       <c r="CJ60" s="34"/>
       <c r="CK60" s="34"/>
       <c r="CL60" s="34"/>
-      <c r="CM60" s="39"/>
+      <c r="CM60" s="34"/>
       <c r="CN60" s="34"/>
       <c r="CO60" s="34"/>
       <c r="CP60" s="34"/>
       <c r="CQ60" s="34"/>
-      <c r="CY60" s="62">
+      <c r="CR60" s="39"/>
+      <c r="CS60" s="34"/>
+      <c r="CT60" s="34"/>
+      <c r="CU60" s="34"/>
+      <c r="CV60" s="34"/>
+      <c r="DD60" s="62">
         <f t="shared" si="31"/>
         <v>8000</v>
       </c>
-      <c r="CZ60" s="62">
+      <c r="DE60" s="62">
         <f t="shared" si="32"/>
         <v>12900</v>
       </c>
-      <c r="DA60" s="62">
+      <c r="DF60" s="62">
         <f t="shared" si="33"/>
         <v>14200</v>
       </c>
     </row>
-    <row r="61" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B61" s="55" t="s">
         <v>544</v>
       </c>
@@ -13118,16 +13403,21 @@
       <c r="CJ61" s="34"/>
       <c r="CK61" s="34"/>
       <c r="CL61" s="34"/>
-      <c r="CM61" s="39"/>
+      <c r="CM61" s="34"/>
       <c r="CN61" s="34"/>
       <c r="CO61" s="34"/>
       <c r="CP61" s="34"/>
       <c r="CQ61" s="34"/>
-      <c r="CY61" s="62"/>
-      <c r="CZ61" s="62"/>
-      <c r="DA61" s="62"/>
-    </row>
-    <row r="62" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="CR61" s="39"/>
+      <c r="CS61" s="34"/>
+      <c r="CT61" s="34"/>
+      <c r="CU61" s="34"/>
+      <c r="CV61" s="34"/>
+      <c r="DD61" s="62"/>
+      <c r="DE61" s="62"/>
+      <c r="DF61" s="62"/>
+    </row>
+    <row r="62" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B62" s="23" t="s">
         <v>374</v>
       </c>
@@ -13241,25 +13531,30 @@
       <c r="CJ62" s="34"/>
       <c r="CK62" s="34"/>
       <c r="CL62" s="34"/>
-      <c r="CM62" s="39"/>
+      <c r="CM62" s="34"/>
       <c r="CN62" s="34"/>
       <c r="CO62" s="34"/>
       <c r="CP62" s="34"/>
       <c r="CQ62" s="34"/>
-      <c r="CY62" s="62">
+      <c r="CR62" s="39"/>
+      <c r="CS62" s="34"/>
+      <c r="CT62" s="34"/>
+      <c r="CU62" s="34"/>
+      <c r="CV62" s="34"/>
+      <c r="DD62" s="62">
         <f t="shared" si="31"/>
         <v>13600</v>
       </c>
-      <c r="CZ62" s="62">
+      <c r="DE62" s="62">
         <f t="shared" si="32"/>
         <v>20600</v>
       </c>
-      <c r="DA62" s="62">
+      <c r="DF62" s="62">
         <f t="shared" si="33"/>
         <v>28500</v>
       </c>
     </row>
-    <row r="63" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B63" s="23" t="s">
         <v>373</v>
       </c>
@@ -13372,25 +13667,30 @@
       <c r="CJ63" s="34"/>
       <c r="CK63" s="34"/>
       <c r="CL63" s="34"/>
-      <c r="CM63" s="39"/>
+      <c r="CM63" s="34"/>
       <c r="CN63" s="34"/>
       <c r="CO63" s="34"/>
       <c r="CP63" s="34"/>
       <c r="CQ63" s="34"/>
-      <c r="CY63" s="62">
+      <c r="CR63" s="39"/>
+      <c r="CS63" s="34"/>
+      <c r="CT63" s="34"/>
+      <c r="CU63" s="34"/>
+      <c r="CV63" s="34"/>
+      <c r="DD63" s="62">
         <f t="shared" si="31"/>
         <v>24700</v>
       </c>
-      <c r="CZ63" s="62">
+      <c r="DE63" s="62">
         <f t="shared" si="32"/>
         <v>25800</v>
       </c>
-      <c r="DA63" s="62">
+      <c r="DF63" s="62">
         <f t="shared" si="33"/>
         <v>26400</v>
       </c>
     </row>
-    <row r="64" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B64" s="23" t="s">
         <v>372</v>
       </c>
@@ -13510,25 +13810,30 @@
       <c r="CJ64" s="34"/>
       <c r="CK64" s="34"/>
       <c r="CL64" s="34"/>
-      <c r="CM64" s="39"/>
+      <c r="CM64" s="34"/>
       <c r="CN64" s="34"/>
       <c r="CO64" s="34"/>
       <c r="CP64" s="34"/>
       <c r="CQ64" s="34"/>
-      <c r="CY64" s="62">
+      <c r="CR64" s="39"/>
+      <c r="CS64" s="34"/>
+      <c r="CT64" s="34"/>
+      <c r="CU64" s="34"/>
+      <c r="CV64" s="34"/>
+      <c r="DD64" s="62">
         <f t="shared" si="31"/>
         <v>34900</v>
       </c>
-      <c r="CZ64" s="62">
+      <c r="DE64" s="62">
         <f t="shared" si="32"/>
         <v>47300</v>
       </c>
-      <c r="DA64" s="62">
+      <c r="DF64" s="62">
         <f t="shared" si="33"/>
         <v>54600</v>
       </c>
     </row>
-    <row r="65" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B65" s="23" t="s">
         <v>371</v>
       </c>
@@ -13648,25 +13953,30 @@
       <c r="CJ65" s="34"/>
       <c r="CK65" s="34"/>
       <c r="CL65" s="34"/>
-      <c r="CM65" s="39"/>
+      <c r="CM65" s="34"/>
       <c r="CN65" s="34"/>
       <c r="CO65" s="34"/>
       <c r="CP65" s="34"/>
       <c r="CQ65" s="34"/>
-      <c r="CY65" s="62">
+      <c r="CR65" s="39"/>
+      <c r="CS65" s="34"/>
+      <c r="CT65" s="34"/>
+      <c r="CU65" s="34"/>
+      <c r="CV65" s="34"/>
+      <c r="DD65" s="62">
         <f t="shared" si="31"/>
         <v>69100</v>
       </c>
-      <c r="CZ65" s="62">
+      <c r="DE65" s="62">
         <f t="shared" si="32"/>
         <v>84100</v>
       </c>
-      <c r="DA65" s="62">
+      <c r="DF65" s="62">
         <f t="shared" si="33"/>
         <v>109500</v>
       </c>
     </row>
-    <row r="66" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B66" s="23" t="s">
         <v>370</v>
       </c>
@@ -13786,25 +14096,30 @@
       <c r="CJ66" s="34"/>
       <c r="CK66" s="34"/>
       <c r="CL66" s="34"/>
-      <c r="CM66" s="39"/>
+      <c r="CM66" s="34"/>
       <c r="CN66" s="34"/>
       <c r="CO66" s="34"/>
       <c r="CP66" s="34"/>
       <c r="CQ66" s="34"/>
-      <c r="CY66" s="62">
+      <c r="CR66" s="39"/>
+      <c r="CS66" s="34"/>
+      <c r="CT66" s="34"/>
+      <c r="CU66" s="34"/>
+      <c r="CV66" s="34"/>
+      <c r="DD66" s="62">
         <f t="shared" si="31"/>
         <v>91200</v>
       </c>
-      <c r="CZ66" s="62">
+      <c r="DE66" s="62">
         <f t="shared" si="32"/>
         <v>92700</v>
       </c>
-      <c r="DA66" s="62">
+      <c r="DF66" s="62">
         <f t="shared" si="33"/>
         <v>87300</v>
       </c>
     </row>
-    <row r="67" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B67" s="23" t="s">
         <v>369</v>
       </c>
@@ -13921,25 +14236,30 @@
       <c r="CJ67" s="34"/>
       <c r="CK67" s="34"/>
       <c r="CL67" s="34"/>
-      <c r="CM67" s="39"/>
+      <c r="CM67" s="34"/>
       <c r="CN67" s="34"/>
       <c r="CO67" s="34"/>
       <c r="CP67" s="34"/>
       <c r="CQ67" s="34"/>
-      <c r="CY67" s="62">
+      <c r="CR67" s="39"/>
+      <c r="CS67" s="34"/>
+      <c r="CT67" s="34"/>
+      <c r="CU67" s="34"/>
+      <c r="CV67" s="34"/>
+      <c r="DD67" s="62">
         <f t="shared" si="31"/>
         <v>31000</v>
       </c>
-      <c r="CZ67" s="62">
+      <c r="DE67" s="62">
         <f t="shared" si="32"/>
         <v>34800</v>
       </c>
-      <c r="DA67" s="62">
+      <c r="DF67" s="62">
         <f t="shared" si="33"/>
         <v>39100</v>
       </c>
     </row>
-    <row r="68" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B68" s="23" t="s">
         <v>368</v>
       </c>
@@ -14058,25 +14378,30 @@
       <c r="CJ68" s="34"/>
       <c r="CK68" s="34"/>
       <c r="CL68" s="34"/>
-      <c r="CM68" s="39"/>
+      <c r="CM68" s="34"/>
       <c r="CN68" s="34"/>
       <c r="CO68" s="34"/>
       <c r="CP68" s="34"/>
       <c r="CQ68" s="34"/>
-      <c r="CY68" s="62">
+      <c r="CR68" s="39"/>
+      <c r="CS68" s="34"/>
+      <c r="CT68" s="34"/>
+      <c r="CU68" s="34"/>
+      <c r="CV68" s="34"/>
+      <c r="DD68" s="62">
         <f t="shared" si="31"/>
         <v>90000</v>
       </c>
-      <c r="CZ68" s="62">
+      <c r="DE68" s="62">
         <f t="shared" si="32"/>
         <v>121400</v>
       </c>
-      <c r="DA68" s="62">
+      <c r="DF68" s="62">
         <f t="shared" si="33"/>
         <v>134000</v>
       </c>
     </row>
-    <row r="69" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B69" s="23" t="s">
         <v>367</v>
       </c>
@@ -14198,25 +14523,30 @@
       <c r="CJ69" s="34"/>
       <c r="CK69" s="34"/>
       <c r="CL69" s="34"/>
-      <c r="CM69" s="39"/>
+      <c r="CM69" s="34"/>
       <c r="CN69" s="34"/>
       <c r="CO69" s="34"/>
       <c r="CP69" s="34"/>
       <c r="CQ69" s="34"/>
-      <c r="CY69" s="62">
+      <c r="CR69" s="39"/>
+      <c r="CS69" s="34"/>
+      <c r="CT69" s="34"/>
+      <c r="CU69" s="34"/>
+      <c r="CV69" s="34"/>
+      <c r="DD69" s="62">
         <f t="shared" si="31"/>
         <v>385900</v>
       </c>
-      <c r="CZ69" s="62">
+      <c r="DE69" s="62">
         <f t="shared" si="32"/>
         <v>522200</v>
       </c>
-      <c r="DA69" s="62">
+      <c r="DF69" s="62">
         <f t="shared" si="33"/>
         <v>644600</v>
       </c>
     </row>
-    <row r="70" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B70" s="23" t="s">
         <v>366</v>
       </c>
@@ -14330,25 +14660,30 @@
       <c r="CJ70" s="34"/>
       <c r="CK70" s="34"/>
       <c r="CL70" s="34"/>
-      <c r="CM70" s="39"/>
+      <c r="CM70" s="34"/>
       <c r="CN70" s="34"/>
       <c r="CO70" s="34"/>
       <c r="CP70" s="34"/>
       <c r="CQ70" s="34"/>
-      <c r="CY70" s="62">
+      <c r="CR70" s="39"/>
+      <c r="CS70" s="34"/>
+      <c r="CT70" s="34"/>
+      <c r="CU70" s="34"/>
+      <c r="CV70" s="34"/>
+      <c r="DD70" s="62">
         <f t="shared" si="31"/>
         <v>9600</v>
       </c>
-      <c r="CZ70" s="62">
+      <c r="DE70" s="62">
         <f t="shared" si="32"/>
         <v>13000</v>
       </c>
-      <c r="DA70" s="62">
+      <c r="DF70" s="62">
         <f t="shared" si="33"/>
         <v>35100</v>
       </c>
     </row>
-    <row r="71" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B71" s="23" t="s">
         <v>365</v>
       </c>
@@ -14462,25 +14797,30 @@
       <c r="CJ71" s="34"/>
       <c r="CK71" s="34"/>
       <c r="CL71" s="34"/>
-      <c r="CM71" s="39"/>
+      <c r="CM71" s="34"/>
       <c r="CN71" s="34"/>
       <c r="CO71" s="34"/>
       <c r="CP71" s="34"/>
       <c r="CQ71" s="34"/>
-      <c r="CY71" s="62">
+      <c r="CR71" s="39"/>
+      <c r="CS71" s="34"/>
+      <c r="CT71" s="34"/>
+      <c r="CU71" s="34"/>
+      <c r="CV71" s="34"/>
+      <c r="DD71" s="62">
         <f t="shared" si="31"/>
         <v>1300</v>
       </c>
-      <c r="CZ71" s="62">
+      <c r="DE71" s="62">
         <f t="shared" si="32"/>
         <v>10500</v>
       </c>
-      <c r="DA71" s="62">
+      <c r="DF71" s="62">
         <f t="shared" si="33"/>
         <v>19100</v>
       </c>
     </row>
-    <row r="72" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B72" s="23" t="s">
         <v>364</v>
       </c>
@@ -14594,25 +14934,30 @@
       <c r="CJ72" s="34"/>
       <c r="CK72" s="34"/>
       <c r="CL72" s="34"/>
-      <c r="CM72" s="39"/>
+      <c r="CM72" s="34"/>
       <c r="CN72" s="34"/>
       <c r="CO72" s="34"/>
       <c r="CP72" s="34"/>
       <c r="CQ72" s="34"/>
-      <c r="CY72" s="62">
+      <c r="CR72" s="39"/>
+      <c r="CS72" s="34"/>
+      <c r="CT72" s="34"/>
+      <c r="CU72" s="34"/>
+      <c r="CV72" s="34"/>
+      <c r="DD72" s="62">
         <f t="shared" si="31"/>
         <v>19300</v>
       </c>
-      <c r="CZ72" s="62">
+      <c r="DE72" s="62">
         <f t="shared" si="32"/>
         <v>18500</v>
       </c>
-      <c r="DA72" s="62">
+      <c r="DF72" s="62">
         <f t="shared" si="33"/>
         <v>17100</v>
       </c>
     </row>
-    <row r="73" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B73" s="23" t="s">
         <v>363</v>
       </c>
@@ -14725,25 +15070,30 @@
       <c r="CJ73" s="34"/>
       <c r="CK73" s="34"/>
       <c r="CL73" s="34"/>
-      <c r="CM73" s="39"/>
+      <c r="CM73" s="34"/>
       <c r="CN73" s="34"/>
       <c r="CO73" s="34"/>
       <c r="CP73" s="34"/>
       <c r="CQ73" s="34"/>
-      <c r="CY73" s="62">
+      <c r="CR73" s="39"/>
+      <c r="CS73" s="34"/>
+      <c r="CT73" s="34"/>
+      <c r="CU73" s="34"/>
+      <c r="CV73" s="34"/>
+      <c r="DD73" s="62">
         <f t="shared" si="31"/>
         <v>26700</v>
       </c>
-      <c r="CZ73" s="62">
+      <c r="DE73" s="62">
         <f t="shared" si="32"/>
         <v>24600</v>
       </c>
-      <c r="DA73" s="62">
+      <c r="DF73" s="62">
         <f t="shared" si="33"/>
         <v>21200</v>
       </c>
     </row>
-    <row r="74" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B74" s="55" t="s">
         <v>542</v>
       </c>
@@ -14840,16 +15190,21 @@
       <c r="CJ74" s="34"/>
       <c r="CK74" s="34"/>
       <c r="CL74" s="34"/>
-      <c r="CM74" s="39"/>
+      <c r="CM74" s="34"/>
       <c r="CN74" s="34"/>
       <c r="CO74" s="34"/>
       <c r="CP74" s="34"/>
       <c r="CQ74" s="34"/>
-      <c r="CY74" s="62"/>
-      <c r="CZ74" s="62"/>
-      <c r="DA74" s="62"/>
-    </row>
-    <row r="75" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="CR74" s="39"/>
+      <c r="CS74" s="34"/>
+      <c r="CT74" s="34"/>
+      <c r="CU74" s="34"/>
+      <c r="CV74" s="34"/>
+      <c r="DD74" s="62"/>
+      <c r="DE74" s="62"/>
+      <c r="DF74" s="62"/>
+    </row>
+    <row r="75" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B75" s="23" t="s">
         <v>362</v>
       </c>
@@ -14963,25 +15318,30 @@
       <c r="CJ75" s="34"/>
       <c r="CK75" s="34"/>
       <c r="CL75" s="34"/>
-      <c r="CM75" s="39"/>
+      <c r="CM75" s="34"/>
       <c r="CN75" s="34"/>
       <c r="CO75" s="34"/>
       <c r="CP75" s="34"/>
       <c r="CQ75" s="34"/>
-      <c r="CY75" s="62">
+      <c r="CR75" s="39"/>
+      <c r="CS75" s="34"/>
+      <c r="CT75" s="34"/>
+      <c r="CU75" s="34"/>
+      <c r="CV75" s="34"/>
+      <c r="DD75" s="62">
         <f t="shared" si="31"/>
         <v>42400</v>
       </c>
-      <c r="CZ75" s="62">
+      <c r="DE75" s="62">
         <f t="shared" si="32"/>
         <v>48400</v>
       </c>
-      <c r="DA75" s="62">
+      <c r="DF75" s="62">
         <f t="shared" si="33"/>
         <v>51200</v>
       </c>
     </row>
-    <row r="76" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B76" s="23" t="s">
         <v>361</v>
       </c>
@@ -15100,25 +15460,30 @@
       <c r="CJ76" s="34"/>
       <c r="CK76" s="34"/>
       <c r="CL76" s="34"/>
-      <c r="CM76" s="39"/>
+      <c r="CM76" s="34"/>
       <c r="CN76" s="34"/>
       <c r="CO76" s="34"/>
       <c r="CP76" s="34"/>
       <c r="CQ76" s="34"/>
-      <c r="CY76" s="62">
-        <f t="shared" ref="CY76:CY88" si="37">SUM(BR76:BU76)</f>
+      <c r="CR76" s="39"/>
+      <c r="CS76" s="34"/>
+      <c r="CT76" s="34"/>
+      <c r="CU76" s="34"/>
+      <c r="CV76" s="34"/>
+      <c r="DD76" s="62">
+        <f t="shared" ref="DD76:DD88" si="37">SUM(BR76:BU76)</f>
         <v>51700</v>
       </c>
-      <c r="CZ76" s="62">
-        <f t="shared" ref="CZ76:CZ88" si="38">SUM(BV76:BY76)</f>
+      <c r="DE76" s="62">
+        <f t="shared" ref="DE76:DE88" si="38">SUM(BV76:BY76)</f>
         <v>66800</v>
       </c>
-      <c r="DA76" s="62">
-        <f t="shared" ref="DA76:DA88" si="39">SUM(BZ76:CC76)</f>
+      <c r="DF76" s="62">
+        <f t="shared" ref="DF76:DF88" si="39">SUM(BZ76:CC76)</f>
         <v>73600</v>
       </c>
     </row>
-    <row r="77" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B77" s="23" t="s">
         <v>360</v>
       </c>
@@ -15238,25 +15603,30 @@
       <c r="CJ77" s="34"/>
       <c r="CK77" s="34"/>
       <c r="CL77" s="34"/>
-      <c r="CM77" s="39"/>
+      <c r="CM77" s="34"/>
       <c r="CN77" s="34"/>
       <c r="CO77" s="34"/>
       <c r="CP77" s="34"/>
       <c r="CQ77" s="34"/>
-      <c r="CY77" s="62">
+      <c r="CR77" s="39"/>
+      <c r="CS77" s="34"/>
+      <c r="CT77" s="34"/>
+      <c r="CU77" s="34"/>
+      <c r="CV77" s="34"/>
+      <c r="DD77" s="62">
         <f t="shared" si="37"/>
         <v>73100</v>
       </c>
-      <c r="CZ77" s="62">
+      <c r="DE77" s="62">
         <f t="shared" si="38"/>
         <v>85300</v>
       </c>
-      <c r="DA77" s="62">
+      <c r="DF77" s="62">
         <f t="shared" si="39"/>
         <v>91500</v>
       </c>
     </row>
-    <row r="78" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B78" s="23" t="s">
         <v>359</v>
       </c>
@@ -15375,25 +15745,30 @@
       <c r="CJ78" s="34"/>
       <c r="CK78" s="34"/>
       <c r="CL78" s="34"/>
-      <c r="CM78" s="39"/>
+      <c r="CM78" s="34"/>
       <c r="CN78" s="34"/>
       <c r="CO78" s="34"/>
       <c r="CP78" s="34"/>
       <c r="CQ78" s="34"/>
-      <c r="CY78" s="62">
+      <c r="CR78" s="39"/>
+      <c r="CS78" s="34"/>
+      <c r="CT78" s="34"/>
+      <c r="CU78" s="34"/>
+      <c r="CV78" s="34"/>
+      <c r="DD78" s="62">
         <f t="shared" si="37"/>
         <v>103300</v>
       </c>
-      <c r="CZ78" s="62">
+      <c r="DE78" s="62">
         <f t="shared" si="38"/>
         <v>151800</v>
       </c>
-      <c r="DA78" s="62">
+      <c r="DF78" s="62">
         <f t="shared" si="39"/>
         <v>178600</v>
       </c>
     </row>
-    <row r="79" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B79" s="23" t="s">
         <v>358</v>
       </c>
@@ -15507,25 +15882,30 @@
       <c r="CJ79" s="34"/>
       <c r="CK79" s="34"/>
       <c r="CL79" s="34"/>
-      <c r="CM79" s="39"/>
+      <c r="CM79" s="34"/>
       <c r="CN79" s="34"/>
       <c r="CO79" s="34"/>
       <c r="CP79" s="34"/>
       <c r="CQ79" s="34"/>
-      <c r="CY79" s="62">
+      <c r="CR79" s="39"/>
+      <c r="CS79" s="34"/>
+      <c r="CT79" s="34"/>
+      <c r="CU79" s="34"/>
+      <c r="CV79" s="34"/>
+      <c r="DD79" s="62">
         <f t="shared" si="37"/>
         <v>31300</v>
       </c>
-      <c r="CZ79" s="62">
+      <c r="DE79" s="62">
         <f t="shared" si="38"/>
         <v>41900</v>
       </c>
-      <c r="DA79" s="62">
+      <c r="DF79" s="62">
         <f t="shared" si="39"/>
         <v>47800</v>
       </c>
     </row>
-    <row r="80" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B80" s="23" t="s">
         <v>357</v>
       </c>
@@ -15622,25 +16002,30 @@
       <c r="CJ80" s="34"/>
       <c r="CK80" s="34"/>
       <c r="CL80" s="34"/>
-      <c r="CM80" s="39"/>
+      <c r="CM80" s="34"/>
       <c r="CN80" s="34"/>
       <c r="CO80" s="34"/>
       <c r="CP80" s="34"/>
       <c r="CQ80" s="34"/>
-      <c r="CY80" s="62">
+      <c r="CR80" s="39"/>
+      <c r="CS80" s="34"/>
+      <c r="CT80" s="34"/>
+      <c r="CU80" s="34"/>
+      <c r="CV80" s="34"/>
+      <c r="DD80" s="62">
         <f t="shared" si="37"/>
         <v>4000</v>
       </c>
-      <c r="CZ80" s="62">
+      <c r="DE80" s="62">
         <f t="shared" si="38"/>
         <v>4400</v>
       </c>
-      <c r="DA80" s="62">
+      <c r="DF80" s="62">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B81" s="23" t="s">
         <v>356</v>
       </c>
@@ -15753,25 +16138,30 @@
       <c r="CJ81" s="34"/>
       <c r="CK81" s="34"/>
       <c r="CL81" s="34"/>
-      <c r="CM81" s="39"/>
+      <c r="CM81" s="34"/>
       <c r="CN81" s="34"/>
       <c r="CO81" s="34"/>
       <c r="CP81" s="34"/>
       <c r="CQ81" s="34"/>
-      <c r="CY81" s="62">
+      <c r="CR81" s="39"/>
+      <c r="CS81" s="34"/>
+      <c r="CT81" s="34"/>
+      <c r="CU81" s="34"/>
+      <c r="CV81" s="34"/>
+      <c r="DD81" s="62">
         <f t="shared" si="37"/>
         <v>17800</v>
       </c>
-      <c r="CZ81" s="62">
+      <c r="DE81" s="62">
         <f t="shared" si="38"/>
         <v>19600</v>
       </c>
-      <c r="DA81" s="62">
+      <c r="DF81" s="62">
         <f t="shared" si="39"/>
         <v>19500</v>
       </c>
     </row>
-    <row r="82" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B82" s="23" t="s">
         <v>355</v>
       </c>
@@ -15885,25 +16275,30 @@
       <c r="CJ82" s="34"/>
       <c r="CK82" s="34"/>
       <c r="CL82" s="34"/>
-      <c r="CM82" s="39"/>
+      <c r="CM82" s="34"/>
       <c r="CN82" s="34"/>
       <c r="CO82" s="34"/>
       <c r="CP82" s="34"/>
       <c r="CQ82" s="34"/>
-      <c r="CY82" s="62">
+      <c r="CR82" s="39"/>
+      <c r="CS82" s="34"/>
+      <c r="CT82" s="34"/>
+      <c r="CU82" s="34"/>
+      <c r="CV82" s="34"/>
+      <c r="DD82" s="62">
         <f t="shared" si="37"/>
         <v>12300</v>
       </c>
-      <c r="CZ82" s="62">
+      <c r="DE82" s="62">
         <f t="shared" si="38"/>
         <v>12800</v>
       </c>
-      <c r="DA82" s="62">
+      <c r="DF82" s="62">
         <f t="shared" si="39"/>
         <v>12100</v>
       </c>
     </row>
-    <row r="83" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B83" s="23" t="s">
         <v>354</v>
       </c>
@@ -16016,25 +16411,30 @@
       <c r="CJ83" s="34"/>
       <c r="CK83" s="34"/>
       <c r="CL83" s="34"/>
-      <c r="CM83" s="39"/>
+      <c r="CM83" s="34"/>
       <c r="CN83" s="34"/>
       <c r="CO83" s="34"/>
       <c r="CP83" s="34"/>
       <c r="CQ83" s="34"/>
-      <c r="CY83" s="62">
+      <c r="CR83" s="39"/>
+      <c r="CS83" s="34"/>
+      <c r="CT83" s="34"/>
+      <c r="CU83" s="34"/>
+      <c r="CV83" s="34"/>
+      <c r="DD83" s="62">
         <f t="shared" si="37"/>
         <v>39200</v>
       </c>
-      <c r="CZ83" s="62">
+      <c r="DE83" s="62">
         <f t="shared" si="38"/>
         <v>41300</v>
       </c>
-      <c r="DA83" s="62">
+      <c r="DF83" s="62">
         <f t="shared" si="39"/>
         <v>40600</v>
       </c>
     </row>
-    <row r="84" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B84" s="55" t="s">
         <v>543</v>
       </c>
@@ -16132,16 +16532,21 @@
       <c r="CJ84" s="34"/>
       <c r="CK84" s="34"/>
       <c r="CL84" s="34"/>
-      <c r="CM84" s="39"/>
+      <c r="CM84" s="34"/>
       <c r="CN84" s="34"/>
       <c r="CO84" s="34"/>
       <c r="CP84" s="34"/>
       <c r="CQ84" s="34"/>
-      <c r="CY84" s="62"/>
-      <c r="CZ84" s="62"/>
-      <c r="DA84" s="62"/>
-    </row>
-    <row r="85" spans="2:106" x14ac:dyDescent="0.2">
+      <c r="CR84" s="39"/>
+      <c r="CS84" s="34"/>
+      <c r="CT84" s="34"/>
+      <c r="CU84" s="34"/>
+      <c r="CV84" s="34"/>
+      <c r="DD84" s="62"/>
+      <c r="DE84" s="62"/>
+      <c r="DF84" s="62"/>
+    </row>
+    <row r="85" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B85" s="23" t="s">
         <v>353</v>
       </c>
@@ -16260,25 +16665,30 @@
       <c r="CJ85" s="34"/>
       <c r="CK85" s="34"/>
       <c r="CL85" s="34"/>
-      <c r="CM85" s="39"/>
+      <c r="CM85" s="34"/>
       <c r="CN85" s="34"/>
       <c r="CO85" s="34"/>
       <c r="CP85" s="34"/>
       <c r="CQ85" s="34"/>
-      <c r="CY85" s="62">
+      <c r="CR85" s="39"/>
+      <c r="CS85" s="34"/>
+      <c r="CT85" s="34"/>
+      <c r="CU85" s="34"/>
+      <c r="CV85" s="34"/>
+      <c r="DD85" s="62">
         <f t="shared" si="37"/>
         <v>60800</v>
       </c>
-      <c r="CZ85" s="62">
+      <c r="DE85" s="62">
         <f t="shared" si="38"/>
         <v>66600</v>
       </c>
-      <c r="DA85" s="62">
+      <c r="DF85" s="62">
         <f t="shared" si="39"/>
         <v>66400</v>
       </c>
     </row>
-    <row r="86" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B86" s="23" t="s">
         <v>352</v>
       </c>
@@ -16400,25 +16810,30 @@
       <c r="CJ86" s="34"/>
       <c r="CK86" s="34"/>
       <c r="CL86" s="34"/>
-      <c r="CM86" s="39"/>
+      <c r="CM86" s="34"/>
       <c r="CN86" s="34"/>
       <c r="CO86" s="34"/>
       <c r="CP86" s="34"/>
       <c r="CQ86" s="34"/>
-      <c r="CY86" s="62">
+      <c r="CR86" s="39"/>
+      <c r="CS86" s="34"/>
+      <c r="CT86" s="34"/>
+      <c r="CU86" s="34"/>
+      <c r="CV86" s="34"/>
+      <c r="DD86" s="62">
         <f t="shared" si="37"/>
         <v>118500</v>
       </c>
-      <c r="CZ86" s="62">
+      <c r="DE86" s="62">
         <f t="shared" si="38"/>
         <v>118200</v>
       </c>
-      <c r="DA86" s="62">
+      <c r="DF86" s="62">
         <f t="shared" si="39"/>
         <v>122900</v>
       </c>
     </row>
-    <row r="87" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B87" s="23" t="s">
         <v>351</v>
       </c>
@@ -16534,25 +16949,30 @@
       <c r="CJ87" s="34"/>
       <c r="CK87" s="34"/>
       <c r="CL87" s="34"/>
-      <c r="CM87" s="39"/>
+      <c r="CM87" s="34"/>
       <c r="CN87" s="34"/>
       <c r="CO87" s="34"/>
       <c r="CP87" s="34"/>
       <c r="CQ87" s="34"/>
-      <c r="CY87" s="62">
+      <c r="CR87" s="39"/>
+      <c r="CS87" s="34"/>
+      <c r="CT87" s="34"/>
+      <c r="CU87" s="34"/>
+      <c r="CV87" s="34"/>
+      <c r="DD87" s="62">
         <f t="shared" si="37"/>
         <v>23200</v>
       </c>
-      <c r="CZ87" s="62">
+      <c r="DE87" s="62">
         <f t="shared" si="38"/>
         <v>22000</v>
       </c>
-      <c r="DA87" s="62">
+      <c r="DF87" s="62">
         <f t="shared" si="39"/>
         <v>35600</v>
       </c>
     </row>
-    <row r="88" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B88" s="23" t="s">
         <v>350</v>
       </c>
@@ -16651,25 +17071,30 @@
       <c r="CJ88" s="34"/>
       <c r="CK88" s="34"/>
       <c r="CL88" s="34"/>
-      <c r="CM88" s="39"/>
+      <c r="CM88" s="34"/>
       <c r="CN88" s="34"/>
       <c r="CO88" s="34"/>
       <c r="CP88" s="34"/>
       <c r="CQ88" s="34"/>
-      <c r="CY88" s="62">
+      <c r="CR88" s="39"/>
+      <c r="CS88" s="34"/>
+      <c r="CT88" s="34"/>
+      <c r="CU88" s="34"/>
+      <c r="CV88" s="34"/>
+      <c r="DD88" s="62">
         <f t="shared" si="37"/>
         <v>1900</v>
       </c>
-      <c r="CZ88" s="62">
+      <c r="DE88" s="62">
         <f t="shared" si="38"/>
         <v>2600</v>
       </c>
-      <c r="DA88" s="62">
+      <c r="DF88" s="62">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B89" s="23" t="s">
         <v>349</v>
       </c>
@@ -16785,25 +17210,30 @@
       <c r="CJ89" s="34"/>
       <c r="CK89" s="34"/>
       <c r="CL89" s="34"/>
-      <c r="CM89" s="39"/>
+      <c r="CM89" s="34"/>
       <c r="CN89" s="34"/>
       <c r="CO89" s="34"/>
       <c r="CP89" s="34"/>
       <c r="CQ89" s="34"/>
-      <c r="CY89" s="62">
-        <f t="shared" ref="CY89" si="41">SUM(BR89:BU89)</f>
+      <c r="CR89" s="39"/>
+      <c r="CS89" s="34"/>
+      <c r="CT89" s="34"/>
+      <c r="CU89" s="34"/>
+      <c r="CV89" s="34"/>
+      <c r="DD89" s="62">
+        <f t="shared" ref="DD89" si="41">SUM(BR89:BU89)</f>
         <v>13000</v>
       </c>
-      <c r="CZ89" s="62">
-        <f t="shared" ref="CZ89" si="42">SUM(BV89:BY89)</f>
+      <c r="DE89" s="62">
+        <f t="shared" ref="DE89" si="42">SUM(BV89:BY89)</f>
         <v>18100</v>
       </c>
-      <c r="DA89" s="62">
-        <f t="shared" ref="DA89" si="43">SUM(BZ89:CC89)</f>
+      <c r="DF89" s="62">
+        <f t="shared" ref="DF89" si="43">SUM(BZ89:CC89)</f>
         <v>20900</v>
       </c>
     </row>
-    <row r="90" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B90" s="55" t="s">
         <v>541</v>
       </c>
@@ -16900,16 +17330,21 @@
       <c r="CJ90" s="34"/>
       <c r="CK90" s="34"/>
       <c r="CL90" s="34"/>
-      <c r="CM90" s="39"/>
+      <c r="CM90" s="34"/>
       <c r="CN90" s="34"/>
       <c r="CO90" s="34"/>
       <c r="CP90" s="34"/>
       <c r="CQ90" s="34"/>
-      <c r="CY90" s="62"/>
-      <c r="CZ90" s="62"/>
-      <c r="DA90" s="62"/>
-    </row>
-    <row r="91" spans="2:106" x14ac:dyDescent="0.2">
+      <c r="CR90" s="39"/>
+      <c r="CS90" s="34"/>
+      <c r="CT90" s="34"/>
+      <c r="CU90" s="34"/>
+      <c r="CV90" s="34"/>
+      <c r="DD90" s="62"/>
+      <c r="DE90" s="62"/>
+      <c r="DF90" s="62"/>
+    </row>
+    <row r="91" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B91" s="23" t="s">
         <v>348</v>
       </c>
@@ -17008,25 +17443,30 @@
       <c r="CJ91" s="34"/>
       <c r="CK91" s="34"/>
       <c r="CL91" s="34"/>
-      <c r="CM91" s="39"/>
+      <c r="CM91" s="34"/>
       <c r="CN91" s="34"/>
       <c r="CO91" s="34"/>
       <c r="CP91" s="34"/>
       <c r="CQ91" s="34"/>
-      <c r="CY91" s="62">
-        <f t="shared" ref="CY91" si="44">SUM(BR91:BU91)</f>
+      <c r="CR91" s="39"/>
+      <c r="CS91" s="34"/>
+      <c r="CT91" s="34"/>
+      <c r="CU91" s="34"/>
+      <c r="CV91" s="34"/>
+      <c r="DD91" s="62">
+        <f t="shared" ref="DD91" si="44">SUM(BR91:BU91)</f>
         <v>20100</v>
       </c>
-      <c r="CZ91" s="62">
-        <f t="shared" ref="CZ91" si="45">SUM(BV91:BY91)</f>
+      <c r="DE91" s="62">
+        <f t="shared" ref="DE91" si="45">SUM(BV91:BY91)</f>
         <v>8400</v>
       </c>
-      <c r="DA91" s="62">
-        <f t="shared" ref="DA91" si="46">SUM(BZ91:CC91)</f>
+      <c r="DF91" s="62">
+        <f t="shared" ref="DF91" si="46">SUM(BZ91:CC91)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B92" s="23" t="s">
         <v>347</v>
       </c>
@@ -17142,25 +17582,30 @@
       <c r="CJ92" s="34"/>
       <c r="CK92" s="34"/>
       <c r="CL92" s="34"/>
-      <c r="CM92" s="39"/>
+      <c r="CM92" s="34"/>
       <c r="CN92" s="34"/>
       <c r="CO92" s="34"/>
       <c r="CP92" s="34"/>
       <c r="CQ92" s="34"/>
-      <c r="CY92" s="62">
-        <f t="shared" ref="CY92" si="47">SUM(BR92:BU92)</f>
+      <c r="CR92" s="39"/>
+      <c r="CS92" s="34"/>
+      <c r="CT92" s="34"/>
+      <c r="CU92" s="34"/>
+      <c r="CV92" s="34"/>
+      <c r="DD92" s="62">
+        <f t="shared" ref="DD92" si="47">SUM(BR92:BU92)</f>
         <v>26400</v>
       </c>
-      <c r="CZ92" s="62">
-        <f t="shared" ref="CZ92" si="48">SUM(BV92:BY92)</f>
+      <c r="DE92" s="62">
+        <f t="shared" ref="DE92" si="48">SUM(BV92:BY92)</f>
         <v>23700</v>
       </c>
-      <c r="DA92" s="62">
-        <f t="shared" ref="DA92" si="49">SUM(BZ92:CC92)</f>
+      <c r="DF92" s="62">
+        <f t="shared" ref="DF92" si="49">SUM(BZ92:CC92)</f>
         <v>29100</v>
       </c>
     </row>
-    <row r="93" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B93" s="23" t="s">
         <v>346</v>
       </c>
@@ -17278,25 +17723,30 @@
       <c r="CJ93" s="34"/>
       <c r="CK93" s="34"/>
       <c r="CL93" s="34"/>
-      <c r="CM93" s="39"/>
+      <c r="CM93" s="34"/>
       <c r="CN93" s="34"/>
       <c r="CO93" s="34"/>
       <c r="CP93" s="34"/>
       <c r="CQ93" s="34"/>
-      <c r="CY93" s="62">
-        <f t="shared" ref="CY93" si="53">SUM(BR93:BU93)</f>
+      <c r="CR93" s="39"/>
+      <c r="CS93" s="34"/>
+      <c r="CT93" s="34"/>
+      <c r="CU93" s="34"/>
+      <c r="CV93" s="34"/>
+      <c r="DD93" s="62">
+        <f t="shared" ref="DD93" si="53">SUM(BR93:BU93)</f>
         <v>40300</v>
       </c>
-      <c r="CZ93" s="62">
-        <f t="shared" ref="CZ93" si="54">SUM(BV93:BY93)</f>
+      <c r="DE93" s="62">
+        <f t="shared" ref="DE93" si="54">SUM(BV93:BY93)</f>
         <v>45500</v>
       </c>
-      <c r="DA93" s="62">
-        <f t="shared" ref="DA93" si="55">SUM(BZ93:CC93)</f>
+      <c r="DF93" s="62">
+        <f t="shared" ref="DF93" si="55">SUM(BZ93:CC93)</f>
         <v>45400</v>
       </c>
     </row>
-    <row r="94" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B94" s="23" t="s">
         <v>345</v>
       </c>
@@ -17417,25 +17867,30 @@
       <c r="CJ94" s="34"/>
       <c r="CK94" s="34"/>
       <c r="CL94" s="34"/>
-      <c r="CM94" s="39"/>
+      <c r="CM94" s="34"/>
       <c r="CN94" s="34"/>
       <c r="CO94" s="34"/>
       <c r="CP94" s="34"/>
       <c r="CQ94" s="34"/>
-      <c r="CY94" s="62">
-        <f t="shared" ref="CY94" si="56">SUM(BR94:BU94)</f>
+      <c r="CR94" s="39"/>
+      <c r="CS94" s="34"/>
+      <c r="CT94" s="34"/>
+      <c r="CU94" s="34"/>
+      <c r="CV94" s="34"/>
+      <c r="DD94" s="62">
+        <f t="shared" ref="DD94" si="56">SUM(BR94:BU94)</f>
         <v>102400</v>
       </c>
-      <c r="CZ94" s="62">
-        <f t="shared" ref="CZ94" si="57">SUM(BV94:BY94)</f>
+      <c r="DE94" s="62">
+        <f t="shared" ref="DE94" si="57">SUM(BV94:BY94)</f>
         <v>108700</v>
       </c>
-      <c r="DA94" s="62">
-        <f t="shared" ref="DA94" si="58">SUM(BZ94:CC94)</f>
+      <c r="DF94" s="62">
+        <f t="shared" ref="DF94" si="58">SUM(BZ94:CC94)</f>
         <v>118400</v>
       </c>
     </row>
-    <row r="95" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B95" s="23" t="s">
         <v>344</v>
       </c>
@@ -17550,25 +18005,30 @@
       <c r="CJ95" s="34"/>
       <c r="CK95" s="34"/>
       <c r="CL95" s="34"/>
-      <c r="CM95" s="39"/>
+      <c r="CM95" s="34"/>
       <c r="CN95" s="34"/>
       <c r="CO95" s="34"/>
       <c r="CP95" s="34"/>
       <c r="CQ95" s="34"/>
-      <c r="CY95" s="62">
-        <f t="shared" ref="CY95" si="59">SUM(BR95:BU95)</f>
+      <c r="CR95" s="39"/>
+      <c r="CS95" s="34"/>
+      <c r="CT95" s="34"/>
+      <c r="CU95" s="34"/>
+      <c r="CV95" s="34"/>
+      <c r="DD95" s="62">
+        <f t="shared" ref="DD95" si="59">SUM(BR95:BU95)</f>
         <v>75700</v>
       </c>
-      <c r="CZ95" s="62">
-        <f t="shared" ref="CZ95" si="60">SUM(BV95:BY95)</f>
+      <c r="DE95" s="62">
+        <f t="shared" ref="DE95" si="60">SUM(BV95:BY95)</f>
         <v>93100</v>
       </c>
-      <c r="DA95" s="62">
-        <f t="shared" ref="DA95" si="61">SUM(BZ95:CC95)</f>
+      <c r="DF95" s="62">
+        <f t="shared" ref="DF95" si="61">SUM(BZ95:CC95)</f>
         <v>119300</v>
       </c>
     </row>
-    <row r="96" spans="2:106" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:111" x14ac:dyDescent="0.25">
       <c r="B96" s="23" t="s">
         <v>338</v>
       </c>
@@ -17683,49 +18143,54 @@
       <c r="CJ96" s="34"/>
       <c r="CK96" s="34"/>
       <c r="CL96" s="34"/>
-      <c r="CM96" s="39"/>
+      <c r="CM96" s="34"/>
       <c r="CN96" s="34"/>
       <c r="CO96" s="34"/>
       <c r="CP96" s="34"/>
       <c r="CQ96" s="34"/>
-      <c r="CR96" s="34">
+      <c r="CR96" s="39"/>
+      <c r="CS96" s="34"/>
+      <c r="CT96" s="34"/>
+      <c r="CU96" s="34"/>
+      <c r="CV96" s="34"/>
+      <c r="CW96" s="34">
         <v>27800</v>
       </c>
-      <c r="CS96" s="34">
+      <c r="CX96" s="34">
         <v>86200</v>
       </c>
-      <c r="CT96" s="34">
+      <c r="CY96" s="34">
         <v>143200</v>
       </c>
-      <c r="CU96" s="14">
+      <c r="CZ96" s="14">
         <v>201400</v>
       </c>
-      <c r="CV96" s="14">
+      <c r="DA96" s="14">
         <v>269200</v>
       </c>
-      <c r="CW96" s="14">
+      <c r="DB96" s="14">
         <v>347200</v>
       </c>
-      <c r="CX96" s="14">
+      <c r="DC96" s="14">
         <v>429281</v>
       </c>
-      <c r="CY96" s="62">
+      <c r="DD96" s="62">
         <f>SUM(BR96:BU96)</f>
         <v>521800</v>
       </c>
-      <c r="CZ96" s="62">
-        <f t="shared" ref="CZ96" si="62">SUM(BV96:BY96)</f>
+      <c r="DE96" s="62">
+        <f t="shared" ref="DE96" si="62">SUM(BV96:BY96)</f>
         <v>702800</v>
       </c>
-      <c r="DA96" s="62">
-        <f t="shared" ref="DA96" si="63">SUM(BZ96:CC96)</f>
+      <c r="DF96" s="62">
+        <f t="shared" ref="DF96" si="63">SUM(BZ96:CC96)</f>
         <v>800900</v>
       </c>
-      <c r="DB96" s="14">
+      <c r="DG96" s="14">
         <v>914000</v>
       </c>
     </row>
-    <row r="97" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B97" s="23"/>
       <c r="F97" s="34"/>
       <c r="G97" s="34"/>
@@ -17804,13 +18269,18 @@
       <c r="CJ97" s="34"/>
       <c r="CK97" s="34"/>
       <c r="CL97" s="34"/>
-      <c r="CM97" s="39"/>
+      <c r="CM97" s="34"/>
       <c r="CN97" s="34"/>
       <c r="CO97" s="34"/>
       <c r="CP97" s="34"/>
       <c r="CQ97" s="34"/>
-    </row>
-    <row r="98" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="CR97" s="39"/>
+      <c r="CS97" s="34"/>
+      <c r="CT97" s="34"/>
+      <c r="CU97" s="34"/>
+      <c r="CV97" s="34"/>
+    </row>
+    <row r="98" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B98" s="23" t="s">
         <v>210</v>
       </c>
@@ -17898,27 +18368,32 @@
       <c r="CK98" s="34"/>
       <c r="CL98" s="34"/>
       <c r="CM98" s="34"/>
-      <c r="CN98" s="34">
-        <f>CM98</f>
-        <v>0</v>
-      </c>
+      <c r="CN98" s="34"/>
       <c r="CO98" s="34"/>
       <c r="CP98" s="34"/>
       <c r="CQ98" s="34"/>
-      <c r="CY98" s="14">
-        <f>CY103-SUM(CY4:CY96)</f>
+      <c r="CR98" s="34"/>
+      <c r="CS98" s="34">
+        <f>CR98</f>
+        <v>0</v>
+      </c>
+      <c r="CT98" s="34"/>
+      <c r="CU98" s="34"/>
+      <c r="CV98" s="34"/>
+      <c r="DD98" s="14">
+        <f>DD103-SUM(DD4:DD96)</f>
         <v>488706</v>
       </c>
-      <c r="CZ98" s="14">
-        <f>CZ103-SUM(CZ4:CZ96)</f>
+      <c r="DE98" s="14">
+        <f>DE103-SUM(DE4:DE96)</f>
         <v>335678</v>
       </c>
-      <c r="DA98" s="14">
-        <f>CZ98</f>
+      <c r="DF98" s="14">
+        <f>DE98</f>
         <v>335678</v>
       </c>
     </row>
-    <row r="99" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
         <v>69</v>
       </c>
@@ -18000,22 +18475,27 @@
       <c r="CI99" s="34"/>
       <c r="CJ99" s="34"/>
       <c r="CK99" s="34"/>
-      <c r="CL99" s="34">
-        <v>30000</v>
-      </c>
+      <c r="CL99" s="34"/>
       <c r="CM99" s="34"/>
       <c r="CN99" s="34"/>
-      <c r="CO99" s="34">
+      <c r="CO99" s="34"/>
+      <c r="CP99" s="34"/>
+      <c r="CQ99" s="34">
+        <v>30000</v>
+      </c>
+      <c r="CR99" s="34"/>
+      <c r="CS99" s="34"/>
+      <c r="CT99" s="34">
         <v>5000</v>
       </c>
-      <c r="CP99" s="34">
+      <c r="CU99" s="34">
         <v>50000</v>
       </c>
-      <c r="CQ99" s="34">
+      <c r="CV99" s="34">
         <v>100000</v>
       </c>
     </row>
-    <row r="100" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
         <v>63</v>
       </c>
@@ -18095,16 +18575,21 @@
       <c r="CI100" s="34"/>
       <c r="CJ100" s="34"/>
       <c r="CK100" s="34"/>
-      <c r="CL100" s="34">
-        <v>0</v>
-      </c>
+      <c r="CL100" s="34"/>
       <c r="CM100" s="34"/>
       <c r="CN100" s="34"/>
       <c r="CO100" s="34"/>
       <c r="CP100" s="34"/>
-      <c r="CQ100" s="34"/>
-    </row>
-    <row r="101" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="CQ100" s="34">
+        <v>0</v>
+      </c>
+      <c r="CR100" s="34"/>
+      <c r="CS100" s="34"/>
+      <c r="CT100" s="34"/>
+      <c r="CU100" s="34"/>
+      <c r="CV100" s="34"/>
+    </row>
+    <row r="101" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B101" s="1" t="s">
         <v>71</v>
       </c>
@@ -18190,8 +18675,13 @@
       <c r="CO101" s="34"/>
       <c r="CP101" s="34"/>
       <c r="CQ101" s="34"/>
-    </row>
-    <row r="102" spans="2:105" x14ac:dyDescent="0.2">
+      <c r="CR101" s="34"/>
+      <c r="CS101" s="34"/>
+      <c r="CT101" s="34"/>
+      <c r="CU101" s="34"/>
+      <c r="CV101" s="34"/>
+    </row>
+    <row r="102" spans="2:110" x14ac:dyDescent="0.25">
       <c r="F102" s="34"/>
       <c r="G102" s="34"/>
       <c r="H102" s="34"/>
@@ -18243,7 +18733,7 @@
       <c r="AM102" s="34"/>
       <c r="AN102" s="34"/>
     </row>
-    <row r="103" spans="2:105" s="16" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:110" s="16" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B103" s="16" t="s">
         <v>56</v>
       </c>
@@ -18294,7 +18784,7 @@
         <v>372493</v>
       </c>
       <c r="Q103" s="32">
-        <f>+CM103-P103-O103-N103</f>
+        <f>+CR103-P103-O103-N103</f>
         <v>338019</v>
       </c>
       <c r="R103" s="32">
@@ -18380,7 +18870,7 @@
       <c r="BP103" s="32"/>
       <c r="BQ103" s="32"/>
       <c r="BR103" s="32">
-        <f t="shared" ref="BR103:CG103" si="64">SUM(BR4:BR96)</f>
+        <f t="shared" ref="BR103:CO103" si="64">SUM(BR4:BR96)</f>
         <v>745200</v>
       </c>
       <c r="BS103" s="32">
@@ -18443,47 +18933,76 @@
         <f t="shared" si="64"/>
         <v>964100</v>
       </c>
-      <c r="CH103" s="32"/>
-      <c r="CI103" s="32"/>
-      <c r="CJ103" s="32"/>
-      <c r="CK103" s="32"/>
+      <c r="CH103" s="32">
+        <f t="shared" si="64"/>
+        <v>14994.444444444447</v>
+      </c>
+      <c r="CI103" s="32">
+        <f t="shared" si="64"/>
+        <v>15602.631578947367</v>
+      </c>
+      <c r="CJ103" s="32">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="CK103" s="32">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
       <c r="CL103" s="32">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="CM103" s="32">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="CN103" s="32">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="CO103" s="32">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="CP103" s="32"/>
+      <c r="CQ103" s="32">
         <v>1538336</v>
       </c>
-      <c r="CM103" s="32">
+      <c r="CR103" s="32">
         <v>1465965</v>
       </c>
-      <c r="CN103" s="32">
-        <f>CN4+CN10+CN15+CN18+SUM(CN23:CN102)</f>
+      <c r="CS103" s="32">
+        <f>CS4+CS10+CS15+CS18+SUM(CS23:CS102)</f>
         <v>1430248</v>
       </c>
-      <c r="CO103" s="32">
-        <f>SUM(CO4:CO101)</f>
+      <c r="CT103" s="32">
+        <f>SUM(CT4:CT101)</f>
         <v>1962325.12162644</v>
       </c>
-      <c r="CP103" s="32">
-        <f>SUM(CP4:CP101)</f>
+      <c r="CU103" s="32">
+        <f>SUM(CU4:CU101)</f>
         <v>1286809.6236819702</v>
       </c>
-      <c r="CQ103" s="32">
-        <f>SUM(CQ4:CQ101)</f>
+      <c r="CV103" s="32">
+        <f>SUM(CV4:CV101)</f>
         <v>1097533.628754145</v>
       </c>
-      <c r="CR103" s="33"/>
-      <c r="CS103" s="33"/>
-      <c r="CT103" s="33"/>
-      <c r="CY103" s="60">
+      <c r="CW103" s="33"/>
+      <c r="CX103" s="33"/>
+      <c r="CY103" s="33"/>
+      <c r="DD103" s="60">
         <v>3569006</v>
       </c>
-      <c r="CZ103" s="60">
+      <c r="DE103" s="60">
         <v>4027478</v>
       </c>
-      <c r="DA103" s="60">
-        <f>SUM(DA4:DA98)</f>
+      <c r="DF103" s="60">
+        <f>SUM(DF4:DF98)</f>
         <v>4291478</v>
       </c>
     </row>
-    <row r="104" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B104" s="1" t="s">
         <v>57</v>
       </c>
@@ -18530,7 +19049,7 @@
         <v>74247</v>
       </c>
       <c r="Q104" s="39">
-        <f>+CM104-P104-O104-N104</f>
+        <f>+CR104-P104-O104-N104</f>
         <v>70435</v>
       </c>
       <c r="R104" s="34">
@@ -18642,36 +19161,41 @@
       <c r="CI104" s="34"/>
       <c r="CJ104" s="34"/>
       <c r="CK104" s="34"/>
-      <c r="CL104" s="34">
+      <c r="CL104" s="34"/>
+      <c r="CM104" s="34"/>
+      <c r="CN104" s="34"/>
+      <c r="CO104" s="34"/>
+      <c r="CP104" s="34"/>
+      <c r="CQ104" s="34">
         <v>289543</v>
       </c>
-      <c r="CM104" s="34">
+      <c r="CR104" s="34">
         <v>285064</v>
       </c>
-      <c r="CN104" s="34">
-        <f>CN103-CN105</f>
+      <c r="CS104" s="34">
+        <f>CS103-CS105</f>
         <v>271747.11999999988</v>
       </c>
-      <c r="CO104" s="34">
-        <f>CO103-CO105</f>
+      <c r="CT104" s="34">
+        <f>CT103-CT105</f>
         <v>372841.77310902346</v>
       </c>
-      <c r="CP104" s="34">
-        <f>CP103-CP105</f>
+      <c r="CU104" s="34">
+        <f>CU103-CU105</f>
         <v>231625.73226275458</v>
       </c>
-      <c r="CQ104" s="34">
-        <f>CQ103-CQ105</f>
+      <c r="CV104" s="34">
+        <f>CV103-CV105</f>
         <v>197556.05317574611</v>
       </c>
-      <c r="CY104" s="14">
+      <c r="DD104" s="14">
         <v>1106846</v>
       </c>
-      <c r="CZ104" s="14">
+      <c r="DE104" s="14">
         <v>1244072</v>
       </c>
     </row>
-    <row r="105" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B105" s="1" t="s">
         <v>58</v>
       </c>
@@ -18837,40 +19361,45 @@
       <c r="CI105" s="34"/>
       <c r="CJ105" s="34"/>
       <c r="CK105" s="34"/>
-      <c r="CL105" s="34">
-        <f>+CL103-CL104</f>
+      <c r="CL105" s="34"/>
+      <c r="CM105" s="34"/>
+      <c r="CN105" s="34"/>
+      <c r="CO105" s="34"/>
+      <c r="CP105" s="34"/>
+      <c r="CQ105" s="34">
+        <f>+CQ103-CQ104</f>
         <v>1248793</v>
       </c>
-      <c r="CM105" s="34">
-        <f>+CM103-CM104</f>
+      <c r="CR105" s="34">
+        <f>+CR103-CR104</f>
         <v>1180901</v>
       </c>
-      <c r="CN105" s="34">
-        <f>CN103*CN119</f>
+      <c r="CS105" s="34">
+        <f>CS103*CS119</f>
         <v>1158500.8800000001</v>
       </c>
-      <c r="CO105" s="34">
-        <f>CO103*CO119</f>
+      <c r="CT105" s="34">
+        <f>CT103*CT119</f>
         <v>1589483.3485174165</v>
       </c>
-      <c r="CP105" s="34">
-        <f>CP103*CP119</f>
+      <c r="CU105" s="34">
+        <f>CU103*CU119</f>
         <v>1055183.8914192156</v>
       </c>
-      <c r="CQ105" s="34">
-        <f>CQ103*CQ119</f>
+      <c r="CV105" s="34">
+        <f>CV103*CV119</f>
         <v>899977.57557839889</v>
       </c>
-      <c r="CY105" s="14">
-        <f>CY103-CY104</f>
+      <c r="DD105" s="14">
+        <f>DD103-DD104</f>
         <v>2462160</v>
       </c>
-      <c r="CZ105" s="14">
-        <f>CZ103-CZ104</f>
+      <c r="DE105" s="14">
+        <f>DE103-DE104</f>
         <v>2783406</v>
       </c>
     </row>
-    <row r="106" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B106" s="1" t="s">
         <v>59</v>
       </c>
@@ -19020,37 +19549,42 @@
       <c r="CI106" s="34"/>
       <c r="CJ106" s="34"/>
       <c r="CK106" s="34"/>
-      <c r="CL106" s="34">
+      <c r="CL106" s="34"/>
+      <c r="CM106" s="34"/>
+      <c r="CN106" s="34"/>
+      <c r="CO106" s="34"/>
+      <c r="CP106" s="34"/>
+      <c r="CQ106" s="34">
         <v>942325</v>
       </c>
-      <c r="CM106" s="34">
-        <f>760690-CM107</f>
+      <c r="CR106" s="34">
+        <f>760690-CR107</f>
         <v>464290</v>
       </c>
-      <c r="CN106" s="34">
-        <f>CM106*0.99</f>
+      <c r="CS106" s="34">
+        <f>CR106*0.99</f>
         <v>459647.1</v>
       </c>
-      <c r="CO106" s="34">
-        <f>CN106*0.8</f>
+      <c r="CT106" s="34">
+        <f>CS106*0.8</f>
         <v>367717.68</v>
       </c>
-      <c r="CP106" s="34">
-        <f>CO106*0.8</f>
+      <c r="CU106" s="34">
+        <f>CT106*0.8</f>
         <v>294174.14400000003</v>
       </c>
-      <c r="CQ106" s="34">
-        <f>CP106*0.8</f>
+      <c r="CV106" s="34">
+        <f>CU106*0.8</f>
         <v>235339.31520000004</v>
       </c>
-      <c r="CY106" s="14">
+      <c r="DD106" s="14">
         <v>886361</v>
       </c>
-      <c r="CZ106" s="14">
+      <c r="DE106" s="14">
         <v>997309</v>
       </c>
     </row>
-    <row r="107" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
         <v>89</v>
       </c>
@@ -19191,26 +19725,31 @@
       <c r="CI107" s="49"/>
       <c r="CJ107" s="49"/>
       <c r="CK107" s="49"/>
-      <c r="CL107" s="49" t="s">
+      <c r="CL107" s="49"/>
+      <c r="CM107" s="49"/>
+      <c r="CN107" s="49"/>
+      <c r="CO107" s="49"/>
+      <c r="CP107" s="49"/>
+      <c r="CQ107" s="49" t="s">
         <v>246</v>
       </c>
-      <c r="CM107" s="49">
+      <c r="CR107" s="49">
         <v>296400</v>
       </c>
-      <c r="CN107" s="49" t="s">
+      <c r="CS107" s="49" t="s">
         <v>247</v>
       </c>
-      <c r="CO107" s="34"/>
-      <c r="CP107" s="34"/>
-      <c r="CQ107" s="34"/>
-      <c r="CY107" s="14">
+      <c r="CT107" s="34"/>
+      <c r="CU107" s="34"/>
+      <c r="CV107" s="34"/>
+      <c r="DD107" s="14">
         <v>526087</v>
       </c>
-      <c r="CZ107" s="14">
+      <c r="DE107" s="14">
         <v>633325</v>
       </c>
     </row>
-    <row r="108" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B108" s="23" t="s">
         <v>185</v>
       </c>
@@ -19368,24 +19907,29 @@
       <c r="CJ108" s="34"/>
       <c r="CK108" s="34"/>
       <c r="CL108" s="34"/>
-      <c r="CM108" s="34">
-        <f>+CM107+CM106</f>
-        <v>760690</v>
-      </c>
+      <c r="CM108" s="34"/>
       <c r="CN108" s="34"/>
       <c r="CO108" s="34"/>
       <c r="CP108" s="34"/>
       <c r="CQ108" s="34"/>
-      <c r="CY108" s="14">
-        <f>CY106+CY107</f>
+      <c r="CR108" s="34">
+        <f>+CR107+CR106</f>
+        <v>760690</v>
+      </c>
+      <c r="CS108" s="34"/>
+      <c r="CT108" s="34"/>
+      <c r="CU108" s="34"/>
+      <c r="CV108" s="34"/>
+      <c r="DD108" s="14">
+        <f>DD106+DD107</f>
         <v>1412448</v>
       </c>
-      <c r="CZ108" s="14">
-        <f>CZ106+CZ107</f>
+      <c r="DE108" s="14">
+        <f>DE106+DE107</f>
         <v>1630634</v>
       </c>
     </row>
-    <row r="109" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B109" s="1" t="s">
         <v>81</v>
       </c>
@@ -19557,40 +20101,45 @@
       <c r="CI109" s="34"/>
       <c r="CJ109" s="34"/>
       <c r="CK109" s="34"/>
-      <c r="CL109" s="34">
-        <f>CL105-CL106</f>
+      <c r="CL109" s="34"/>
+      <c r="CM109" s="34"/>
+      <c r="CN109" s="34"/>
+      <c r="CO109" s="34"/>
+      <c r="CP109" s="34"/>
+      <c r="CQ109" s="34">
+        <f>CQ105-CQ106</f>
         <v>306468</v>
       </c>
-      <c r="CM109" s="34">
-        <f>+CM105-CM108</f>
+      <c r="CR109" s="34">
+        <f>+CR105-CR108</f>
         <v>420211</v>
       </c>
-      <c r="CN109" s="34">
-        <f>CN105-CN106-CN107</f>
+      <c r="CS109" s="34">
+        <f>CS105-CS106-CS107</f>
         <v>398853.78000000014</v>
       </c>
-      <c r="CO109" s="34">
-        <f>CO105-CO106-CO107</f>
+      <c r="CT109" s="34">
+        <f>CT105-CT106-CT107</f>
         <v>1221765.6685174166</v>
       </c>
-      <c r="CP109" s="34">
-        <f>CP105-CP106-CP107</f>
+      <c r="CU109" s="34">
+        <f>CU105-CU106-CU107</f>
         <v>761009.74741921551</v>
       </c>
-      <c r="CQ109" s="34">
-        <f>CQ105-CQ106-CQ107</f>
+      <c r="CV109" s="34">
+        <f>CV105-CV106-CV107</f>
         <v>664638.26037839882</v>
       </c>
-      <c r="CY109" s="14">
-        <f>CY105-CY108</f>
+      <c r="DD109" s="14">
+        <f>DD105-DD108</f>
         <v>1049712</v>
       </c>
-      <c r="CZ109" s="14">
-        <f>CZ105-CZ108</f>
+      <c r="DE109" s="14">
+        <f>DE105-DE108</f>
         <v>1152772</v>
       </c>
     </row>
-    <row r="110" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="s">
         <v>80</v>
       </c>
@@ -19722,32 +20271,37 @@
       <c r="CK110" s="34"/>
       <c r="CL110" s="34"/>
       <c r="CM110" s="34"/>
-      <c r="CN110" s="34">
-        <f>CM122*$CT$115</f>
+      <c r="CN110" s="34"/>
+      <c r="CO110" s="34"/>
+      <c r="CP110" s="34"/>
+      <c r="CQ110" s="34"/>
+      <c r="CR110" s="34"/>
+      <c r="CS110" s="34">
+        <f>CR122*$CY$115</f>
         <v>0</v>
       </c>
-      <c r="CO110" s="34">
-        <f>CN122*$CT$115</f>
+      <c r="CT110" s="34">
+        <f>CS122*$CY$115</f>
         <v>0</v>
       </c>
-      <c r="CP110" s="34">
-        <f>CO122*$CT$115</f>
+      <c r="CU110" s="34">
+        <f>CT122*$CY$115</f>
         <v>0</v>
       </c>
-      <c r="CQ110" s="34">
-        <f>CP122*$CT$115</f>
+      <c r="CV110" s="34">
+        <f>CU122*$CY$115</f>
         <v>0</v>
       </c>
-      <c r="CY110" s="14">
+      <c r="DD110" s="14">
         <f>43123-159075+23700-166607</f>
         <v>-258859</v>
       </c>
-      <c r="CZ110" s="14">
+      <c r="DE110" s="14">
         <f>25424-145247+62913-169698</f>
         <v>-226608</v>
       </c>
     </row>
-    <row r="111" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B111" s="1" t="s">
         <v>82</v>
       </c>
@@ -19892,40 +20446,45 @@
       <c r="CI111" s="34"/>
       <c r="CJ111" s="34"/>
       <c r="CK111" s="34"/>
-      <c r="CL111" s="34">
-        <f t="shared" ref="CL111:CQ111" si="73">CL109+CL110</f>
+      <c r="CL111" s="34"/>
+      <c r="CM111" s="34"/>
+      <c r="CN111" s="34"/>
+      <c r="CO111" s="34"/>
+      <c r="CP111" s="34"/>
+      <c r="CQ111" s="34">
+        <f t="shared" ref="CQ111:CV111" si="73">CQ109+CQ110</f>
         <v>306468</v>
       </c>
-      <c r="CM111" s="34">
+      <c r="CR111" s="34">
         <f t="shared" si="73"/>
         <v>420211</v>
       </c>
-      <c r="CN111" s="34">
+      <c r="CS111" s="34">
         <f t="shared" si="73"/>
         <v>398853.78000000014</v>
       </c>
-      <c r="CO111" s="34">
+      <c r="CT111" s="34">
         <f t="shared" si="73"/>
         <v>1221765.6685174166</v>
       </c>
-      <c r="CP111" s="34">
+      <c r="CU111" s="34">
         <f t="shared" si="73"/>
         <v>761009.74741921551</v>
       </c>
-      <c r="CQ111" s="34">
+      <c r="CV111" s="34">
         <f t="shared" si="73"/>
         <v>664638.26037839882</v>
       </c>
-      <c r="CY111" s="14">
-        <f>CY109+CY110</f>
+      <c r="DD111" s="14">
+        <f>DD109+DD110</f>
         <v>790853</v>
       </c>
-      <c r="CZ111" s="14">
-        <f>CZ109+CZ110</f>
+      <c r="DE111" s="14">
+        <f>DE109+DE110</f>
         <v>926164</v>
       </c>
     </row>
-    <row r="112" spans="2:105" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:110" x14ac:dyDescent="0.25">
       <c r="B112" s="1" t="s">
         <v>60</v>
       </c>
@@ -20077,38 +20636,43 @@
       <c r="CI112" s="34"/>
       <c r="CJ112" s="34"/>
       <c r="CK112" s="34"/>
-      <c r="CL112" s="34">
-        <f t="shared" ref="CL112:CQ112" si="74">CL111*0.3</f>
+      <c r="CL112" s="34"/>
+      <c r="CM112" s="34"/>
+      <c r="CN112" s="34"/>
+      <c r="CO112" s="34"/>
+      <c r="CP112" s="34"/>
+      <c r="CQ112" s="34">
+        <f t="shared" ref="CQ112:CV112" si="74">CQ111*0.3</f>
         <v>91940.4</v>
       </c>
-      <c r="CM112" s="34">
+      <c r="CR112" s="34">
         <f t="shared" si="74"/>
         <v>126063.29999999999</v>
       </c>
-      <c r="CN112" s="34">
+      <c r="CS112" s="34">
         <f t="shared" si="74"/>
         <v>119656.13400000003</v>
       </c>
-      <c r="CO112" s="34">
+      <c r="CT112" s="34">
         <f t="shared" si="74"/>
         <v>366529.70055522496</v>
       </c>
-      <c r="CP112" s="34">
+      <c r="CU112" s="34">
         <f t="shared" si="74"/>
         <v>228302.92422576464</v>
       </c>
-      <c r="CQ112" s="34">
+      <c r="CV112" s="34">
         <f t="shared" si="74"/>
         <v>199391.47811351964</v>
       </c>
-      <c r="CY112" s="14">
+      <c r="DD112" s="14">
         <v>72405</v>
       </c>
-      <c r="CZ112" s="14">
+      <c r="DE112" s="14">
         <v>58052</v>
       </c>
     </row>
-    <row r="113" spans="2:128" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:133" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B113" s="23" t="s">
         <v>100</v>
       </c>
@@ -20264,50 +20828,50 @@
       <c r="CI113" s="39"/>
       <c r="CJ113" s="39"/>
       <c r="CK113" s="39"/>
-      <c r="CL113" s="39">
-        <f t="shared" ref="CL113:CQ113" si="77">CL111-CL112</f>
+      <c r="CL113" s="39"/>
+      <c r="CM113" s="39"/>
+      <c r="CN113" s="39"/>
+      <c r="CO113" s="39"/>
+      <c r="CP113" s="39"/>
+      <c r="CQ113" s="39">
+        <f t="shared" ref="CQ113:CV113" si="77">CQ111-CQ112</f>
         <v>214527.6</v>
       </c>
-      <c r="CM113" s="39">
+      <c r="CR113" s="39">
         <f t="shared" si="77"/>
         <v>294147.7</v>
       </c>
-      <c r="CN113" s="39">
+      <c r="CS113" s="39">
         <f t="shared" si="77"/>
         <v>279197.64600000012</v>
       </c>
-      <c r="CO113" s="39">
+      <c r="CT113" s="39">
         <f t="shared" si="77"/>
         <v>855235.96796219167</v>
       </c>
-      <c r="CP113" s="39">
+      <c r="CU113" s="39">
         <f t="shared" si="77"/>
         <v>532706.82319345092</v>
       </c>
-      <c r="CQ113" s="39">
+      <c r="CV113" s="39">
         <f t="shared" si="77"/>
         <v>465246.78226487921</v>
       </c>
-      <c r="CR113" s="39"/>
-      <c r="CS113" s="39"/>
-      <c r="CT113" s="39"/>
-      <c r="CU113" s="39"/>
-      <c r="CV113" s="39"/>
       <c r="CW113" s="39"/>
       <c r="CX113" s="39"/>
-      <c r="CY113" s="39">
-        <f>CY111-CY112</f>
-        <v>718448</v>
-      </c>
-      <c r="CZ113" s="39">
-        <f>CZ111-CZ112</f>
-        <v>868112</v>
-      </c>
+      <c r="CY113" s="39"/>
+      <c r="CZ113" s="39"/>
       <c r="DA113" s="39"/>
       <c r="DB113" s="39"/>
       <c r="DC113" s="39"/>
-      <c r="DD113" s="39"/>
-      <c r="DE113" s="39"/>
+      <c r="DD113" s="39">
+        <f>DD111-DD112</f>
+        <v>718448</v>
+      </c>
+      <c r="DE113" s="39">
+        <f>DE111-DE112</f>
+        <v>868112</v>
+      </c>
       <c r="DF113" s="39"/>
       <c r="DG113" s="39"/>
       <c r="DH113" s="39"/>
@@ -20327,8 +20891,13 @@
       <c r="DV113" s="39"/>
       <c r="DW113" s="39"/>
       <c r="DX113" s="39"/>
-    </row>
-    <row r="114" spans="2:128" x14ac:dyDescent="0.2">
+      <c r="DY113" s="39"/>
+      <c r="DZ113" s="39"/>
+      <c r="EA113" s="39"/>
+      <c r="EB113" s="39"/>
+      <c r="EC113" s="39"/>
+    </row>
+    <row r="114" spans="2:133" ht="13" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
         <v>191</v>
       </c>
@@ -20395,36 +20964,36 @@
         <f>+BW113/BW115</f>
         <v>-393.15270618556701</v>
       </c>
-      <c r="CL114" s="43">
-        <f t="shared" ref="CL114:CQ114" si="79">CL113/CL115</f>
+      <c r="CQ114" s="43">
+        <f t="shared" ref="CQ114:CV114" si="79">CQ113/CQ115</f>
         <v>271.77295998375644</v>
       </c>
-      <c r="CM114" s="43">
+      <c r="CR114" s="43">
         <f t="shared" si="79"/>
         <v>372.63135939594991</v>
       </c>
-      <c r="CN114" s="46">
+      <c r="CS114" s="46">
         <f t="shared" si="79"/>
         <v>353.69237416824694</v>
       </c>
-      <c r="CO114" s="46">
+      <c r="CT114" s="46">
         <f t="shared" si="79"/>
         <v>1083.4276159428157</v>
       </c>
-      <c r="CP114" s="46">
+      <c r="CU114" s="46">
         <f t="shared" si="79"/>
         <v>674.84215476127656</v>
       </c>
-      <c r="CQ114" s="46">
+      <c r="CV114" s="46">
         <f t="shared" si="79"/>
         <v>589.38261604613422</v>
       </c>
-      <c r="CZ114" s="47">
-        <f>CZ113/CZ115</f>
+      <c r="DE114" s="47">
+        <f>DE113/DE115</f>
         <v>559.35051546391753</v>
       </c>
     </row>
-    <row r="115" spans="2:128" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:133" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B115" s="14" t="s">
         <v>48</v>
       </c>
@@ -20548,43 +21117,48 @@
       <c r="CI115" s="34"/>
       <c r="CJ115" s="34"/>
       <c r="CK115" s="34"/>
-      <c r="CL115" s="34">
+      <c r="CL115" s="34"/>
+      <c r="CM115" s="34"/>
+      <c r="CN115" s="34"/>
+      <c r="CO115" s="34"/>
+      <c r="CP115" s="34"/>
+      <c r="CQ115" s="34">
         <f>789.666095-0.302797</f>
         <v>789.36329799999999</v>
       </c>
-      <c r="CM115" s="34">
+      <c r="CR115" s="34">
         <f>789.666095-0.286209</f>
         <v>789.37988600000006</v>
       </c>
-      <c r="CN115" s="34">
+      <c r="CS115" s="34">
         <f>789.666095-0.286209</f>
         <v>789.37988600000006</v>
       </c>
-      <c r="CO115" s="34">
+      <c r="CT115" s="34">
         <f>789.666095-0.286209</f>
         <v>789.37988600000006</v>
       </c>
-      <c r="CP115" s="34">
+      <c r="CU115" s="34">
         <f>789.666095-0.286209</f>
         <v>789.37988600000006</v>
       </c>
-      <c r="CQ115" s="34">
+      <c r="CV115" s="34">
         <f>789.666095-0.286209</f>
         <v>789.37988600000006</v>
       </c>
-      <c r="CR115" s="34"/>
-      <c r="CS115" s="45"/>
-      <c r="CT115" s="48"/>
-      <c r="CZ115" s="14">
+      <c r="CW115" s="34"/>
+      <c r="CX115" s="45"/>
+      <c r="CY115" s="48"/>
+      <c r="DE115" s="14">
         <v>1552</v>
       </c>
     </row>
-    <row r="116" spans="2:128" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:133" x14ac:dyDescent="0.25">
       <c r="P116" s="39"/>
-      <c r="CS116" s="45"/>
-      <c r="CT116" s="48"/>
-    </row>
-    <row r="117" spans="2:128" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="CX116" s="45"/>
+      <c r="CY116" s="48"/>
+    </row>
+    <row r="117" spans="2:133" s="16" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B117" s="16" t="s">
         <v>61</v>
       </c>
@@ -20750,43 +21324,48 @@
       <c r="CI117" s="40"/>
       <c r="CJ117" s="40"/>
       <c r="CK117" s="40"/>
-      <c r="CL117" s="40">
-        <f>CL103/AW103-1</f>
+      <c r="CL117" s="40"/>
+      <c r="CM117" s="40"/>
+      <c r="CN117" s="40"/>
+      <c r="CO117" s="40"/>
+      <c r="CP117" s="40"/>
+      <c r="CQ117" s="40">
+        <f>CQ103/AW103-1</f>
         <v>0.11895257491998845</v>
       </c>
-      <c r="CM117" s="40">
-        <f>CM103/CL103-1</f>
+      <c r="CR117" s="40">
+        <f>CR103/CQ103-1</f>
         <v>-4.7044988871091875E-2</v>
       </c>
-      <c r="CN117" s="40">
-        <f>CN103/CM103-1</f>
+      <c r="CS117" s="40">
+        <f>CS103/CR103-1</f>
         <v>-2.4364156033738871E-2</v>
       </c>
-      <c r="CO117" s="40">
-        <f>CO103/CN103-1</f>
+      <c r="CT117" s="40">
+        <f>CT103/CS103-1</f>
         <v>0.37201738553484431</v>
       </c>
-      <c r="CP117" s="40">
-        <f>CP103/CO103-1</f>
+      <c r="CU117" s="40">
+        <f>CU103/CT103-1</f>
         <v>-0.34424239413730795</v>
       </c>
-      <c r="CQ117" s="40">
-        <f>CQ103/CP103-1</f>
+      <c r="CV117" s="40">
+        <f>CV103/CU103-1</f>
         <v>-0.1470893529582461</v>
       </c>
-      <c r="CR117" s="33"/>
-      <c r="CS117" s="45"/>
-      <c r="CT117" s="48"/>
-      <c r="CZ117" s="68">
-        <f>CZ103/CY103-1</f>
+      <c r="CW117" s="33"/>
+      <c r="CX117" s="45"/>
+      <c r="CY117" s="48"/>
+      <c r="DE117" s="68">
+        <f>DE103/DD103-1</f>
         <v>0.12845929651000865</v>
       </c>
-      <c r="DA117" s="68">
-        <f>DA103/CZ103-1</f>
+      <c r="DF117" s="68">
+        <f>DF103/DE103-1</f>
         <v>6.5549706292622911E-2</v>
       </c>
     </row>
-    <row r="118" spans="2:128" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:133" x14ac:dyDescent="0.25">
       <c r="B118" s="1" t="s">
         <v>111</v>
       </c>
@@ -20870,34 +21449,39 @@
       <c r="CI118" s="38"/>
       <c r="CJ118" s="38"/>
       <c r="CK118" s="38"/>
-      <c r="CL118" s="38">
-        <f>CL113/AW113-1</f>
+      <c r="CL118" s="38"/>
+      <c r="CM118" s="38"/>
+      <c r="CN118" s="38"/>
+      <c r="CO118" s="38"/>
+      <c r="CP118" s="38"/>
+      <c r="CQ118" s="38">
+        <f>CQ113/AW113-1</f>
         <v>-0.45689215189873411</v>
       </c>
-      <c r="CM118" s="38">
-        <f>CM113/CL113-1</f>
+      <c r="CR118" s="38">
+        <f>CR113/CQ113-1</f>
         <v>0.37114152211650153</v>
       </c>
-      <c r="CN118" s="38">
-        <f>CN113/CM113-1</f>
+      <c r="CS118" s="38">
+        <f>CS113/CR113-1</f>
         <v>-5.0824990302490547E-2</v>
       </c>
-      <c r="CO118" s="38">
-        <f>CO113/CN113-1</f>
+      <c r="CT118" s="38">
+        <f>CT113/CS113-1</f>
         <v>2.0631919008450068</v>
       </c>
-      <c r="CP118" s="38">
-        <f>CP113/CO113-1</f>
+      <c r="CU118" s="38">
+        <f>CU113/CT113-1</f>
         <v>-0.37712298926955223</v>
       </c>
-      <c r="CQ118" s="38">
-        <f>CQ113/CP113-1</f>
+      <c r="CV118" s="38">
+        <f>CV113/CU113-1</f>
         <v>-0.12663633727115564</v>
       </c>
-      <c r="CS118" s="45"/>
-      <c r="CT118" s="34"/>
-    </row>
-    <row r="119" spans="2:128" x14ac:dyDescent="0.2">
+      <c r="CX118" s="45"/>
+      <c r="CY118" s="34"/>
+    </row>
+    <row r="119" spans="2:133" x14ac:dyDescent="0.25">
       <c r="B119" s="1" t="s">
         <v>77</v>
       </c>
@@ -21038,28 +21622,33 @@
       <c r="CI119" s="38"/>
       <c r="CJ119" s="38"/>
       <c r="CK119" s="38"/>
-      <c r="CL119" s="38">
-        <f>CL105/CL103</f>
+      <c r="CL119" s="38"/>
+      <c r="CM119" s="38"/>
+      <c r="CN119" s="38"/>
+      <c r="CO119" s="38"/>
+      <c r="CP119" s="38"/>
+      <c r="CQ119" s="38">
+        <f>CQ105/CQ103</f>
         <v>0.81178169138601708</v>
       </c>
-      <c r="CM119" s="38">
-        <f>CM105/CM103</f>
+      <c r="CR119" s="38">
+        <f>CR105/CR103</f>
         <v>0.80554515285153461</v>
       </c>
-      <c r="CN119" s="38">
+      <c r="CS119" s="38">
         <v>0.81</v>
       </c>
-      <c r="CO119" s="38">
+      <c r="CT119" s="38">
         <v>0.81</v>
       </c>
-      <c r="CP119" s="38">
+      <c r="CU119" s="38">
         <v>0.82</v>
       </c>
-      <c r="CQ119" s="38">
+      <c r="CV119" s="38">
         <v>0.82</v>
       </c>
     </row>
-    <row r="120" spans="2:128" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:133" x14ac:dyDescent="0.25">
       <c r="B120" s="23" t="s">
         <v>243</v>
       </c>
@@ -21174,32 +21763,37 @@
       <c r="CI120" s="38"/>
       <c r="CJ120" s="38"/>
       <c r="CK120" s="38"/>
-      <c r="CL120" s="38">
-        <f t="shared" ref="CL120:CQ120" si="86">CL106/CL103</f>
+      <c r="CL120" s="38"/>
+      <c r="CM120" s="38"/>
+      <c r="CN120" s="38"/>
+      <c r="CO120" s="38"/>
+      <c r="CP120" s="38"/>
+      <c r="CQ120" s="38">
+        <f t="shared" ref="CQ120:CV120" si="86">CQ106/CQ103</f>
         <v>0.61256123499677573</v>
       </c>
-      <c r="CM120" s="38">
+      <c r="CR120" s="38">
         <f t="shared" si="86"/>
         <v>0.3167128819583005</v>
       </c>
-      <c r="CN120" s="38">
+      <c r="CS120" s="38">
         <f t="shared" si="86"/>
         <v>0.32137580335718002</v>
       </c>
-      <c r="CO120" s="38">
+      <c r="CT120" s="38">
         <f t="shared" si="86"/>
         <v>0.18738876445470129</v>
       </c>
-      <c r="CP120" s="38">
+      <c r="CU120" s="38">
         <f t="shared" si="86"/>
         <v>0.22860735464370757</v>
       </c>
-      <c r="CQ120" s="38">
+      <c r="CV120" s="38">
         <f t="shared" si="86"/>
         <v>0.21442560759358531</v>
       </c>
     </row>
-    <row r="121" spans="2:128" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:133" x14ac:dyDescent="0.25">
       <c r="B121" s="55" t="s">
         <v>536</v>
       </c>
@@ -21279,7 +21873,7 @@
       <c r="AM121" s="38"/>
       <c r="AN121" s="38"/>
     </row>
-    <row r="122" spans="2:128" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:133" x14ac:dyDescent="0.25">
       <c r="B122" s="23" t="s">
         <v>53</v>
       </c>
@@ -21327,33 +21921,38 @@
       <c r="CJ122" s="34"/>
       <c r="CK122" s="34"/>
       <c r="CL122" s="34"/>
-      <c r="CM122" s="34">
+      <c r="CM122" s="34"/>
+      <c r="CN122" s="34"/>
+      <c r="CO122" s="34"/>
+      <c r="CP122" s="34"/>
+      <c r="CQ122" s="34"/>
+      <c r="CR122" s="34">
         <v>976000</v>
       </c>
-      <c r="CN122" s="34">
-        <f>CM122+CN113</f>
+      <c r="CS122" s="34">
+        <f>CR122+CS113</f>
         <v>1255197.6460000002</v>
       </c>
-      <c r="CO122" s="34">
-        <f>CN122+CO113</f>
+      <c r="CT122" s="34">
+        <f>CS122+CT113</f>
         <v>2110433.6139621921</v>
       </c>
-      <c r="CP122" s="34">
-        <f>CO122+CP113</f>
+      <c r="CU122" s="34">
+        <f>CT122+CU113</f>
         <v>2643140.437155643</v>
       </c>
-      <c r="CQ122" s="34">
-        <f>CP122+CQ113</f>
+      <c r="CV122" s="34">
+        <f>CU122+CV113</f>
         <v>3108387.2194205225</v>
       </c>
     </row>
-    <row r="123" spans="2:128" x14ac:dyDescent="0.2">
-      <c r="CN123" s="34"/>
-      <c r="CO123" s="34"/>
-      <c r="CP123" s="34"/>
-      <c r="CQ123" s="34"/>
-    </row>
-    <row r="124" spans="2:128" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:133" x14ac:dyDescent="0.25">
+      <c r="CS123" s="34"/>
+      <c r="CT123" s="34"/>
+      <c r="CU123" s="34"/>
+      <c r="CV123" s="34"/>
+    </row>
+    <row r="124" spans="2:133" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B124" s="14" t="s">
         <v>219</v>
       </c>
@@ -21444,21 +22043,26 @@
       <c r="CI124" s="34"/>
       <c r="CJ124" s="34"/>
       <c r="CK124" s="34"/>
-      <c r="CL124" s="34">
-        <v>326273</v>
-      </c>
-      <c r="CM124" s="34">
-        <v>381168</v>
-      </c>
+      <c r="CL124" s="34"/>
+      <c r="CM124" s="34"/>
       <c r="CN124" s="34"/>
       <c r="CO124" s="34"/>
       <c r="CP124" s="34"/>
-      <c r="CQ124" s="34"/>
-      <c r="CR124" s="34"/>
+      <c r="CQ124" s="34">
+        <v>326273</v>
+      </c>
+      <c r="CR124" s="34">
+        <v>381168</v>
+      </c>
       <c r="CS124" s="34"/>
       <c r="CT124" s="34"/>
-    </row>
-    <row r="125" spans="2:128" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="CU124" s="34"/>
+      <c r="CV124" s="34"/>
+      <c r="CW124" s="34"/>
+      <c r="CX124" s="34"/>
+      <c r="CY124" s="34"/>
+    </row>
+    <row r="125" spans="2:133" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B125" s="14" t="s">
         <v>220</v>
       </c>
@@ -21549,21 +22153,26 @@
       <c r="CI125" s="34"/>
       <c r="CJ125" s="34"/>
       <c r="CK125" s="34"/>
-      <c r="CL125" s="34">
-        <v>39464</v>
-      </c>
-      <c r="CM125" s="34">
-        <v>86960</v>
-      </c>
+      <c r="CL125" s="34"/>
+      <c r="CM125" s="34"/>
       <c r="CN125" s="34"/>
       <c r="CO125" s="34"/>
       <c r="CP125" s="34"/>
-      <c r="CQ125" s="34"/>
-      <c r="CR125" s="34"/>
+      <c r="CQ125" s="34">
+        <v>39464</v>
+      </c>
+      <c r="CR125" s="34">
+        <v>86960</v>
+      </c>
       <c r="CS125" s="34"/>
       <c r="CT125" s="34"/>
-    </row>
-    <row r="126" spans="2:128" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="CU125" s="34"/>
+      <c r="CV125" s="34"/>
+      <c r="CW125" s="34"/>
+      <c r="CX125" s="34"/>
+      <c r="CY125" s="34"/>
+    </row>
+    <row r="126" spans="2:133" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B126" s="14" t="s">
         <v>221</v>
       </c>
@@ -21654,23 +22263,28 @@
       <c r="CI126" s="34"/>
       <c r="CJ126" s="34"/>
       <c r="CK126" s="34"/>
-      <c r="CL126" s="34">
-        <f>CL124-CL125</f>
-        <v>286809</v>
-      </c>
-      <c r="CM126" s="34">
-        <f>CM124-CM125</f>
-        <v>294208</v>
-      </c>
+      <c r="CL126" s="34"/>
+      <c r="CM126" s="34"/>
       <c r="CN126" s="34"/>
       <c r="CO126" s="34"/>
       <c r="CP126" s="34"/>
-      <c r="CQ126" s="34"/>
-      <c r="CR126" s="34"/>
+      <c r="CQ126" s="34">
+        <f>CQ124-CQ125</f>
+        <v>286809</v>
+      </c>
+      <c r="CR126" s="34">
+        <f>CR124-CR125</f>
+        <v>294208</v>
+      </c>
       <c r="CS126" s="34"/>
       <c r="CT126" s="34"/>
-    </row>
-    <row r="130" spans="2:104" x14ac:dyDescent="0.2">
+      <c r="CU126" s="34"/>
+      <c r="CV126" s="34"/>
+      <c r="CW126" s="34"/>
+      <c r="CX126" s="34"/>
+      <c r="CY126" s="34"/>
+    </row>
+    <row r="130" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B130" s="23" t="s">
         <v>238</v>
       </c>
@@ -21686,7 +22300,7 @@
         <v>162300</v>
       </c>
     </row>
-    <row r="131" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B131" s="23" t="s">
         <v>240</v>
       </c>
@@ -21702,7 +22316,7 @@
         <v>112800</v>
       </c>
     </row>
-    <row r="132" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B132" s="23" t="s">
         <v>239</v>
       </c>
@@ -21718,7 +22332,7 @@
         <v>36700</v>
       </c>
     </row>
-    <row r="133" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:109" x14ac:dyDescent="0.25">
       <c r="R133" s="34">
         <f>+R44+R8+R14+R22</f>
         <v>5200</v>
@@ -21731,157 +22345,157 @@
         <v>6100</v>
       </c>
     </row>
-    <row r="135" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B135" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="CZ135" s="14">
+      <c r="DE135" s="14">
         <f>533530+99174+20174+279683</f>
         <v>932561</v>
       </c>
     </row>
-    <row r="136" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B136" s="55" t="s">
         <v>426</v>
       </c>
-      <c r="CZ136" s="14">
+      <c r="DE136" s="14">
         <v>649429</v>
       </c>
     </row>
-    <row r="137" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B137" s="55" t="s">
         <v>427</v>
       </c>
-      <c r="CZ137" s="14">
+      <c r="DE137" s="14">
         <v>986457</v>
       </c>
     </row>
-    <row r="138" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B138" s="55" t="s">
         <v>428</v>
       </c>
-      <c r="CZ138" s="14">
+      <c r="DE138" s="14">
         <f>160868+15235</f>
         <v>176103</v>
       </c>
     </row>
-    <row r="139" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B139" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="CZ139" s="14">
+      <c r="DE139" s="14">
         <f>32264+366003</f>
         <v>398267</v>
       </c>
     </row>
-    <row r="140" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B140" s="55" t="s">
         <v>432</v>
       </c>
-      <c r="CZ140" s="14">
+      <c r="DE140" s="14">
         <v>63325</v>
       </c>
     </row>
-    <row r="141" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B141" s="55" t="s">
         <v>431</v>
       </c>
-      <c r="CZ141" s="14">
+      <c r="DE141" s="14">
         <v>1691229</v>
       </c>
     </row>
-    <row r="142" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B142" s="55" t="s">
         <v>430</v>
       </c>
-      <c r="CZ142" s="14">
+      <c r="DE142" s="14">
         <f>4790723+4269657</f>
         <v>9060380</v>
       </c>
     </row>
-    <row r="143" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B143" s="55" t="s">
         <v>429</v>
       </c>
-      <c r="CZ143" s="14">
-        <f>SUM(CZ135:CZ142)</f>
+      <c r="DE143" s="14">
+        <f>SUM(DE135:DE142)</f>
         <v>13957751</v>
       </c>
     </row>
-    <row r="145" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B145" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="CZ145" s="14">
+      <c r="DE145" s="14">
         <f>339600+4042741+534269+185537</f>
         <v>5102147</v>
       </c>
     </row>
-    <row r="146" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B146" s="55" t="s">
         <v>433</v>
       </c>
-      <c r="CZ146" s="14">
+      <c r="DE146" s="14">
         <f>566689+144</f>
         <v>566833</v>
       </c>
     </row>
-    <row r="147" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B147" s="55" t="s">
         <v>434</v>
       </c>
-      <c r="CZ147" s="62">
+      <c r="DE147" s="62">
         <f>508360+55969</f>
         <v>564329</v>
       </c>
     </row>
-    <row r="148" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B148" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="CZ148" s="14">
+      <c r="DE148" s="14">
         <f>232377+270620+24558</f>
         <v>527555</v>
       </c>
     </row>
-    <row r="149" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B149" s="55" t="s">
         <v>435</v>
       </c>
-      <c r="CZ149" s="14">
+      <c r="DE149" s="14">
         <v>649233</v>
       </c>
     </row>
-    <row r="150" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B150" s="55" t="s">
         <v>436</v>
       </c>
-      <c r="CZ150" s="14">
+      <c r="DE150" s="14">
         <v>65389</v>
       </c>
     </row>
-    <row r="151" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B151" s="55" t="s">
         <v>437</v>
       </c>
-      <c r="CZ151" s="14">
+      <c r="DE151" s="14">
         <v>127594</v>
       </c>
     </row>
-    <row r="152" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B152" s="55" t="s">
         <v>438</v>
       </c>
-      <c r="CZ152" s="14">
+      <c r="DE152" s="14">
         <v>6354672</v>
       </c>
     </row>
-    <row r="153" spans="2:104" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:109" x14ac:dyDescent="0.25">
       <c r="B153" s="55" t="s">
         <v>439</v>
       </c>
-      <c r="CZ153" s="14">
-        <f>SUM(CZ145:CZ152)</f>
+      <c r="DE153" s="14">
+        <f>SUM(DE145:DE152)</f>
         <v>13957752</v>
       </c>
     </row>
@@ -21901,17 +22515,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51C7B1F-3C55-44F8-A636-0828C64E1C02}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="54" t="s">
         <v>388</v>
       </c>
@@ -21919,7 +22533,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="54" t="s">
         <v>389</v>
       </c>
@@ -21927,7 +22541,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="54" t="s">
         <v>1</v>
       </c>
@@ -21946,19 +22560,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -21966,7 +22580,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -21974,7 +22588,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
@@ -21982,7 +22596,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
@@ -22003,18 +22617,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>11</v>
       </c>
@@ -22035,19 +22649,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="12.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -22055,7 +22669,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
@@ -22063,7 +22677,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
@@ -22084,19 +22698,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="13.54296875" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -22104,7 +22718,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
@@ -22112,7 +22726,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
@@ -22120,7 +22734,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -22128,7 +22742,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>54</v>
       </c>
@@ -22136,7 +22750,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>102</v>
       </c>
@@ -22144,7 +22758,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>3</v>
       </c>
@@ -22152,22 +22766,22 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C11" s="21" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
         <v>126</v>
       </c>
@@ -22186,19 +22800,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="12.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -22206,7 +22820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
@@ -22214,7 +22828,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>102</v>
       </c>
@@ -22222,7 +22836,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
@@ -22230,7 +22844,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>46</v>
       </c>
@@ -22238,7 +22852,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>54</v>
       </c>
@@ -22246,12 +22860,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
@@ -22382,18 +22996,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22413,18 +23027,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F1151A-1AB6-4EC7-9FA4-3C32E8ADF199}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FDDB01B-6A67-42CA-B809-AEC97CEC78B0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F1151A-1AB6-4EC7-9FA4-3C32E8ADF199}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>